--- a/ssp_modeling/scenario_mapping/ssp_mexico_transformation_strategy_pemex_vf.xlsx
+++ b/ssp_modeling/scenario_mapping/ssp_mexico_transformation_strategy_pemex_vf.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10118"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10125"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fabianfuentes/git/ssp_mexico/ssp_modeling/scenario_mapping/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44E16879-6081-2D45-8B3C-CEC2DC80C259}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{380E4F41-8222-A948-83C9-402D348E6745}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-51200" yWindow="-7160" windowWidth="25600" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-45240" yWindow="-7160" windowWidth="40640" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
     <sheet name="yaml" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">main!$A$1:$O$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">main!$A$1:$P$64</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1">yaml!$A$1:$D$62</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="724" uniqueCount="417">
   <si>
     <t>subsector</t>
   </si>
@@ -1332,6 +1332,9 @@
   </si>
   <si>
     <t>transformation_enfu_adj_prices.yaml</t>
+  </si>
+  <si>
+    <t>strategy_6</t>
   </si>
 </sst>
 </file>
@@ -1486,7 +1489,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1611,7 +1614,6 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1930,10 +1932,10 @@
     <col min="9" max="10" width="35" style="4" hidden="1" customWidth="1"/>
     <col min="11" max="11" width="31.5" style="31" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="19.83203125" style="30" customWidth="1"/>
-    <col min="13" max="15" width="18.5" style="32" customWidth="1"/>
+    <col min="13" max="16" width="18.5" style="32" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="4" customFormat="1" ht="65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" s="4" customFormat="1" ht="65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>203</v>
       </c>
@@ -1979,8 +1981,11 @@
       <c r="O1" s="35" t="s">
         <v>412</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" s="4" customFormat="1" ht="154.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P1" s="35" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" s="4" customFormat="1" ht="154.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="9" t="s">
         <v>208</v>
       </c>
@@ -2018,8 +2023,11 @@
       <c r="O2" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" s="4" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P2" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" s="4" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="9" t="s">
         <v>208</v>
       </c>
@@ -2057,8 +2065,11 @@
       <c r="O3" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" s="4" customFormat="1" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P3" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" s="4" customFormat="1" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="9" t="s">
         <v>208</v>
       </c>
@@ -2094,8 +2105,11 @@
       <c r="O4" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" s="4" customFormat="1" ht="100.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P4" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" s="4" customFormat="1" ht="100.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="9" t="s">
         <v>208</v>
       </c>
@@ -2133,8 +2147,11 @@
       <c r="O5" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" s="4" customFormat="1" ht="154.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P5" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" s="4" customFormat="1" ht="154.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="9" t="s">
         <v>208</v>
       </c>
@@ -2174,8 +2191,11 @@
       <c r="O6" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" s="4" customFormat="1" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P6" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" s="4" customFormat="1" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="19" t="s">
         <v>222</v>
       </c>
@@ -2207,8 +2227,9 @@
       <c r="M7" s="13"/>
       <c r="N7" s="13"/>
       <c r="O7" s="13"/>
-    </row>
-    <row r="8" spans="1:15" s="4" customFormat="1" ht="91.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P7" s="13"/>
+    </row>
+    <row r="8" spans="1:16" s="4" customFormat="1" ht="91.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="9" t="s">
         <v>222</v>
       </c>
@@ -2250,8 +2271,11 @@
       <c r="O8" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P8" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
         <v>222</v>
       </c>
@@ -2291,8 +2315,11 @@
       <c r="O9" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P9" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="9" t="s">
         <v>222</v>
       </c>
@@ -2332,8 +2359,9 @@
       <c r="O10" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P10" s="13"/>
+    </row>
+    <row r="11" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="9" t="s">
         <v>222</v>
       </c>
@@ -2369,8 +2397,11 @@
       <c r="O11" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:15" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P11" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="9" t="s">
         <v>222</v>
       </c>
@@ -2406,8 +2437,11 @@
       <c r="O12" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P12" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="9" t="s">
         <v>222</v>
       </c>
@@ -2447,8 +2481,11 @@
       <c r="O13" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P13" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="9" t="s">
         <v>222</v>
       </c>
@@ -2490,8 +2527,11 @@
       <c r="O14" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P14" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="9" t="s">
         <v>222</v>
       </c>
@@ -2527,8 +2567,11 @@
       <c r="O15" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P15" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="9" t="s">
         <v>51</v>
       </c>
@@ -2568,8 +2611,11 @@
       <c r="O16" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:15" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P16" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="9" t="s">
         <v>51</v>
       </c>
@@ -2611,8 +2657,11 @@
       <c r="O17" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:15" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P17" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="9" t="s">
         <v>51</v>
       </c>
@@ -2652,8 +2701,11 @@
       <c r="O18" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:15" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P18" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="9" t="s">
         <v>51</v>
       </c>
@@ -2691,8 +2743,11 @@
       <c r="O19" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:15" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P19" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="9" t="s">
         <v>51</v>
       </c>
@@ -2728,8 +2783,11 @@
       <c r="O20" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:15" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P20" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="9" t="s">
         <v>51</v>
       </c>
@@ -2765,8 +2823,11 @@
       <c r="O21" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:15" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P21" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="9" t="s">
         <v>208</v>
       </c>
@@ -2806,8 +2867,11 @@
       <c r="O22" s="13">
         <v>0.9</v>
       </c>
-    </row>
-    <row r="23" spans="1:15" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P22" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="9" t="s">
         <v>208</v>
       </c>
@@ -2847,8 +2911,11 @@
       <c r="O23" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:15" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P23" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="9" t="s">
         <v>208</v>
       </c>
@@ -2888,8 +2955,11 @@
       <c r="O24" s="13">
         <v>0.9</v>
       </c>
-    </row>
-    <row r="25" spans="1:15" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P24" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="9" t="s">
         <v>208</v>
       </c>
@@ -2929,8 +2999,11 @@
       <c r="O25" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="1:15" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P25" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="9" t="s">
         <v>208</v>
       </c>
@@ -2968,8 +3041,11 @@
       <c r="O26" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:15" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P26" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="9" t="s">
         <v>208</v>
       </c>
@@ -3007,8 +3083,11 @@
       <c r="O27" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="1:15" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P27" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="9" t="s">
         <v>208</v>
       </c>
@@ -3044,8 +3123,11 @@
       <c r="O28" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:15" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P28" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="9" t="s">
         <v>208</v>
       </c>
@@ -3081,8 +3163,11 @@
       <c r="O29" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="1:15" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P29" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="9" t="s">
         <v>208</v>
       </c>
@@ -3118,8 +3203,11 @@
       <c r="O30" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="31" spans="1:15" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P30" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="9" t="s">
         <v>208</v>
       </c>
@@ -3157,8 +3245,11 @@
       <c r="O31" s="13">
         <v>2</v>
       </c>
-    </row>
-    <row r="32" spans="1:15" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P31" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="9" t="s">
         <v>208</v>
       </c>
@@ -3198,8 +3289,11 @@
       <c r="O32" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:15" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P32" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="9" t="s">
         <v>305</v>
       </c>
@@ -3235,8 +3329,11 @@
       <c r="O33" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="34" spans="1:15" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P33" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="9" t="s">
         <v>305</v>
       </c>
@@ -3272,8 +3369,11 @@
       <c r="O34" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="35" spans="1:15" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P34" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="9" t="s">
         <v>222</v>
       </c>
@@ -3309,8 +3409,11 @@
       <c r="O35" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="1:15" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P35" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="9" t="s">
         <v>222</v>
       </c>
@@ -3346,8 +3449,11 @@
       <c r="O36" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="37" spans="1:15" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P36" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="9" t="s">
         <v>222</v>
       </c>
@@ -3383,8 +3489,11 @@
       <c r="O37" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="38" spans="1:15" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P37" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="9" t="s">
         <v>208</v>
       </c>
@@ -3420,8 +3529,11 @@
       <c r="O38" s="13">
         <v>2</v>
       </c>
-    </row>
-    <row r="39" spans="1:15" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P38" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="9" t="s">
         <v>208</v>
       </c>
@@ -3457,8 +3569,11 @@
       <c r="O39" s="13">
         <v>2</v>
       </c>
-    </row>
-    <row r="40" spans="1:15" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P39" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="9" t="s">
         <v>222</v>
       </c>
@@ -3492,7 +3607,7 @@
         <v>10</v>
       </c>
       <c r="M40" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N40" s="13">
         <v>3</v>
@@ -3500,8 +3615,11 @@
       <c r="O40" s="13">
         <v>3</v>
       </c>
-    </row>
-    <row r="41" spans="1:15" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P40" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="9" t="s">
         <v>222</v>
       </c>
@@ -3541,8 +3659,11 @@
       <c r="O41" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="42" spans="1:15" s="4" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P41" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" s="4" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="9" t="s">
         <v>222</v>
       </c>
@@ -3582,8 +3703,11 @@
       <c r="O42" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="43" spans="1:15" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P42" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="9" t="s">
         <v>222</v>
       </c>
@@ -3619,8 +3743,11 @@
       <c r="O43" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="1:15" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P43" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="9" t="s">
         <v>222</v>
       </c>
@@ -3656,8 +3783,11 @@
       <c r="O44" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="45" spans="1:15" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P44" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="9" t="s">
         <v>222</v>
       </c>
@@ -3697,8 +3827,11 @@
       <c r="O45" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="46" spans="1:15" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P45" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="9" t="s">
         <v>222</v>
       </c>
@@ -3738,8 +3871,11 @@
       <c r="O46" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="47" spans="1:15" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P46" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="9" t="s">
         <v>222</v>
       </c>
@@ -3777,8 +3913,11 @@
       <c r="O47" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="48" spans="1:15" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P47" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="9" t="s">
         <v>222</v>
       </c>
@@ -3818,6 +3957,9 @@
       <c r="O48" s="13">
         <v>1</v>
       </c>
+      <c r="P48" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="49" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="9" t="s">
@@ -3859,6 +4001,9 @@
       <c r="O49" s="13">
         <v>1</v>
       </c>
+      <c r="P49" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="50" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="9" t="s">
@@ -3898,6 +4043,9 @@
         <v>1</v>
       </c>
       <c r="O50" s="13">
+        <v>1</v>
+      </c>
+      <c r="P50" s="13">
         <v>1</v>
       </c>
     </row>
@@ -3937,6 +4085,9 @@
       <c r="O51" s="13">
         <v>1</v>
       </c>
+      <c r="P51" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="52" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="9" t="s">
@@ -3978,6 +4129,9 @@
       <c r="O52" s="13">
         <v>1</v>
       </c>
+      <c r="P52" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="53" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="9" t="s">
@@ -4019,6 +4173,9 @@
       <c r="O53" s="13">
         <v>1</v>
       </c>
+      <c r="P53" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="54" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="9" t="s">
@@ -4060,6 +4217,9 @@
       <c r="O54" s="13">
         <v>1</v>
       </c>
+      <c r="P54" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="55" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="9" t="s">
@@ -4101,6 +4261,9 @@
       <c r="O55" s="13">
         <v>1</v>
       </c>
+      <c r="P55" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="56" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="9" t="s">
@@ -4140,7 +4303,10 @@
         <v>1.5</v>
       </c>
       <c r="O56" s="13">
-        <v>1</v>
+        <v>1.5</v>
+      </c>
+      <c r="P56" s="13">
+        <v>1.5</v>
       </c>
     </row>
     <row r="57" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
@@ -4179,6 +4345,9 @@
       <c r="O57" s="13">
         <v>1</v>
       </c>
+      <c r="P57" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="58" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="9" t="s">
@@ -4218,6 +4387,9 @@
         <v>1</v>
       </c>
       <c r="O58" s="13">
+        <v>1</v>
+      </c>
+      <c r="P58" s="13">
         <v>1</v>
       </c>
     </row>
@@ -4257,6 +4429,9 @@
       <c r="O59" s="13">
         <v>1</v>
       </c>
+      <c r="P59" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="60" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="9" t="s">
@@ -4287,11 +4462,16 @@
       <c r="L60" s="10">
         <v>10</v>
       </c>
-      <c r="M60" s="13"/>
+      <c r="M60" s="13">
+        <v>1</v>
+      </c>
       <c r="N60" s="13">
         <v>1</v>
       </c>
       <c r="O60" s="13">
+        <v>1</v>
+      </c>
+      <c r="P60" s="13">
         <v>1</v>
       </c>
     </row>
@@ -4335,6 +4515,9 @@
       <c r="O61" s="13">
         <v>1</v>
       </c>
+      <c r="P61" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="62" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="9" t="s">
@@ -4376,6 +4559,9 @@
       <c r="O62" s="13">
         <v>1</v>
       </c>
+      <c r="P62" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="63" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A63" s="9" t="s">
@@ -4415,7 +4601,7 @@
       <c r="O63" s="13">
         <v>1</v>
       </c>
-      <c r="P63" s="42"/>
+      <c r="P63" s="13"/>
     </row>
     <row r="64" spans="1:16" ht="52" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="9" t="s">
@@ -4451,8 +4637,9 @@
       <c r="M64" s="13"/>
       <c r="N64" s="13"/>
       <c r="O64" s="13"/>
-    </row>
-    <row r="65" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P64" s="13"/>
+    </row>
+    <row r="65" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="16"/>
       <c r="B65" s="16"/>
       <c r="C65" s="16"/>
@@ -4468,11 +4655,12 @@
       <c r="M65" s="25"/>
       <c r="N65" s="25"/>
       <c r="O65" s="25"/>
+      <c r="P65" s="25"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O64" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:P64" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="M8">
-    <cfRule type="colorScale" priority="22">
+    <cfRule type="colorScale" priority="29">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4484,7 +4672,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M13">
-    <cfRule type="colorScale" priority="21">
+    <cfRule type="colorScale" priority="28">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4496,7 +4684,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M15">
-    <cfRule type="colorScale" priority="20">
+    <cfRule type="colorScale" priority="27">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4508,7 +4696,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M46">
-    <cfRule type="colorScale" priority="29">
+    <cfRule type="colorScale" priority="36">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4520,7 +4708,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M65:M1048576 M1:M7 M47:M62 M9:M12 M14 M16:M45 M63:O64">
-    <cfRule type="colorScale" priority="69">
+    <cfRule type="colorScale" priority="76">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4532,7 +4720,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="colorScale" priority="77">
+    <cfRule type="colorScale" priority="84">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4544,7 +4732,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N65:N1048576">
-    <cfRule type="colorScale" priority="17">
+    <cfRule type="colorScale" priority="24">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4555,8 +4743,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:O6 N8:O62">
-    <cfRule type="colorScale" priority="78">
+  <conditionalFormatting sqref="N2:O6 N8:O55 N57:O62">
+    <cfRule type="colorScale" priority="85">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4567,8 +4755,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O1">
-    <cfRule type="colorScale" priority="26">
+  <conditionalFormatting sqref="N56:P56">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4580,7 +4768,55 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O65:O1048576">
-    <cfRule type="colorScale" priority="53">
+    <cfRule type="colorScale" priority="60">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O1:P1">
+    <cfRule type="colorScale" priority="33">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P2:P6 P8:P55 P57:P62">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P63:P64">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P65:P1048576">
+    <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>

--- a/ssp_modeling/scenario_mapping/ssp_mexico_transformation_strategy_pemex_vf.xlsx
+++ b/ssp_modeling/scenario_mapping/ssp_mexico_transformation_strategy_pemex_vf.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10208"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fabianfuentes/git/ssp_mexico/ssp_modeling/scenario_mapping/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{380E4F41-8222-A948-83C9-402D348E6745}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95BCC82F-D1AC-5B48-9C5F-3D727F893176}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-45240" yWindow="-7160" windowWidth="40640" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-34340" yWindow="-620" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -1344,7 +1344,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0%"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1396,6 +1396,14 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1410,7 +1418,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -1485,6 +1493,47 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1518,16 +1567,10 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1593,9 +1636,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1613,6 +1653,15 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1930,16 +1979,16 @@
     <col min="7" max="7" width="47.5" style="4" hidden="1" customWidth="1"/>
     <col min="8" max="8" width="48.5" style="4" hidden="1" customWidth="1"/>
     <col min="9" max="10" width="35" style="4" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="31.5" style="31" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.83203125" style="30" customWidth="1"/>
-    <col min="13" max="16" width="18.5" style="32" customWidth="1"/>
+    <col min="11" max="11" width="31.5" style="29" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.83203125" style="28" customWidth="1"/>
+    <col min="13" max="16" width="18.5" style="30" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" s="4" customFormat="1" ht="65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="31" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="5" t="s">
@@ -1972,16 +2021,16 @@
       <c r="L1" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="M1" s="35" t="s">
+      <c r="M1" s="40" t="s">
         <v>410</v>
       </c>
-      <c r="N1" s="35" t="s">
+      <c r="N1" s="40" t="s">
         <v>411</v>
       </c>
-      <c r="O1" s="35" t="s">
+      <c r="O1" s="40" t="s">
         <v>412</v>
       </c>
-      <c r="P1" s="35" t="s">
+      <c r="P1" s="40" t="s">
         <v>416</v>
       </c>
     </row>
@@ -1989,13 +2038,13 @@
       <c r="A2" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="39" t="s">
+      <c r="C2" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="36" t="s">
+      <c r="D2" s="33" t="s">
         <v>6</v>
       </c>
       <c r="E2" s="9" t="s">
@@ -2004,26 +2053,26 @@
       <c r="F2" s="9" t="s">
         <v>210</v>
       </c>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
       <c r="I2" s="9"/>
       <c r="J2" s="9"/>
-      <c r="K2" s="12">
+      <c r="K2" s="11">
         <v>0.45</v>
       </c>
-      <c r="L2" s="10">
-        <v>10</v>
-      </c>
-      <c r="M2" s="13">
-        <v>1</v>
-      </c>
-      <c r="N2" s="13">
-        <v>1</v>
-      </c>
-      <c r="O2" s="13">
-        <v>1</v>
-      </c>
-      <c r="P2" s="13">
+      <c r="L2" s="39">
+        <v>10</v>
+      </c>
+      <c r="M2" s="41">
+        <v>1</v>
+      </c>
+      <c r="N2" s="41">
+        <v>1</v>
+      </c>
+      <c r="O2" s="41">
+        <v>1</v>
+      </c>
+      <c r="P2" s="41">
         <v>1</v>
       </c>
     </row>
@@ -2031,41 +2080,41 @@
       <c r="A3" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="B3" s="34" t="s">
+      <c r="B3" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="40" t="s">
+      <c r="C3" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="37" t="s">
+      <c r="D3" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="12" t="s">
         <v>211</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="12" t="s">
         <v>212</v>
       </c>
       <c r="G3" s="9"/>
       <c r="H3" s="9"/>
       <c r="I3" s="9"/>
       <c r="J3" s="9"/>
-      <c r="K3" s="15">
+      <c r="K3" s="13">
         <v>0.5</v>
       </c>
-      <c r="L3" s="10">
-        <v>10</v>
-      </c>
-      <c r="M3" s="13">
-        <v>1</v>
-      </c>
-      <c r="N3" s="13">
-        <v>1</v>
-      </c>
-      <c r="O3" s="13">
-        <v>1</v>
-      </c>
-      <c r="P3" s="13">
+      <c r="L3" s="39">
+        <v>10</v>
+      </c>
+      <c r="M3" s="41">
+        <v>1</v>
+      </c>
+      <c r="N3" s="41">
+        <v>1</v>
+      </c>
+      <c r="O3" s="41">
+        <v>1</v>
+      </c>
+      <c r="P3" s="41">
         <v>1</v>
       </c>
     </row>
@@ -2073,13 +2122,13 @@
       <c r="A4" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="B4" s="23" t="s">
+      <c r="B4" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="39" t="s">
+      <c r="C4" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="36" t="s">
+      <c r="D4" s="33" t="s">
         <v>12</v>
       </c>
       <c r="E4" s="9" t="s">
@@ -2092,20 +2141,20 @@
       <c r="H4" s="9"/>
       <c r="I4" s="9"/>
       <c r="J4" s="9"/>
-      <c r="K4" s="15">
+      <c r="K4" s="13">
         <v>0.3</v>
       </c>
-      <c r="L4" s="10">
-        <v>10</v>
-      </c>
-      <c r="M4" s="13"/>
-      <c r="N4" s="13">
-        <v>1</v>
-      </c>
-      <c r="O4" s="13">
-        <v>1</v>
-      </c>
-      <c r="P4" s="13">
+      <c r="L4" s="39">
+        <v>10</v>
+      </c>
+      <c r="M4" s="41"/>
+      <c r="N4" s="41">
+        <v>1</v>
+      </c>
+      <c r="O4" s="41">
+        <v>1</v>
+      </c>
+      <c r="P4" s="41">
         <v>1</v>
       </c>
     </row>
@@ -2113,13 +2162,13 @@
       <c r="A5" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="39" t="s">
+      <c r="C5" s="36" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="36" t="s">
+      <c r="D5" s="33" t="s">
         <v>15</v>
       </c>
       <c r="E5" s="9" t="s">
@@ -2128,26 +2177,26 @@
       <c r="F5" s="9" t="s">
         <v>216</v>
       </c>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="10"/>
       <c r="I5" s="9"/>
       <c r="J5" s="9"/>
-      <c r="K5" s="17" t="s">
+      <c r="K5" s="15" t="s">
         <v>217</v>
       </c>
-      <c r="L5" s="10">
-        <v>10</v>
-      </c>
-      <c r="M5" s="13">
-        <v>1</v>
-      </c>
-      <c r="N5" s="13">
-        <v>1</v>
-      </c>
-      <c r="O5" s="13">
-        <v>1</v>
-      </c>
-      <c r="P5" s="13">
+      <c r="L5" s="39">
+        <v>10</v>
+      </c>
+      <c r="M5" s="41">
+        <v>1</v>
+      </c>
+      <c r="N5" s="41">
+        <v>1</v>
+      </c>
+      <c r="O5" s="41">
+        <v>1</v>
+      </c>
+      <c r="P5" s="41">
         <v>1</v>
       </c>
     </row>
@@ -2155,19 +2204,19 @@
       <c r="A6" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="39" t="s">
+      <c r="C6" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="36" t="s">
+      <c r="D6" s="33" t="s">
         <v>18</v>
       </c>
       <c r="E6" s="9" t="s">
         <v>218</v>
       </c>
-      <c r="F6" s="18" t="s">
+      <c r="F6" s="16" t="s">
         <v>219</v>
       </c>
       <c r="G6" s="9"/>
@@ -2178,37 +2227,37 @@
       <c r="J6" s="9" t="s">
         <v>221</v>
       </c>
-      <c r="K6" s="15">
+      <c r="K6" s="13">
         <v>0.2</v>
       </c>
-      <c r="L6" s="10">
-        <v>10</v>
-      </c>
-      <c r="M6" s="13"/>
-      <c r="N6" s="13">
-        <v>1</v>
-      </c>
-      <c r="O6" s="13">
-        <v>1</v>
-      </c>
-      <c r="P6" s="13">
+      <c r="L6" s="39">
+        <v>10</v>
+      </c>
+      <c r="M6" s="41"/>
+      <c r="N6" s="41">
+        <v>1</v>
+      </c>
+      <c r="O6" s="41">
+        <v>1</v>
+      </c>
+      <c r="P6" s="41">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:16" s="4" customFormat="1" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="17" t="s">
         <v>222</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="B7" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="41" t="s">
+      <c r="C7" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="38" t="s">
+      <c r="D7" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="E7" s="17" t="s">
         <v>223</v>
       </c>
       <c r="F7" s="9" t="s">
@@ -2218,28 +2267,28 @@
       <c r="H7" s="9"/>
       <c r="I7" s="9"/>
       <c r="J7" s="9"/>
-      <c r="K7" s="20">
+      <c r="K7" s="18">
         <v>50</v>
       </c>
-      <c r="L7" s="10">
-        <v>10</v>
-      </c>
-      <c r="M7" s="13"/>
-      <c r="N7" s="13"/>
-      <c r="O7" s="13"/>
-      <c r="P7" s="13"/>
+      <c r="L7" s="39">
+        <v>10</v>
+      </c>
+      <c r="M7" s="41"/>
+      <c r="N7" s="41"/>
+      <c r="O7" s="41"/>
+      <c r="P7" s="41"/>
     </row>
     <row r="8" spans="1:16" s="4" customFormat="1" ht="91.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="B8" s="23" t="s">
+      <c r="B8" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="39" t="s">
+      <c r="C8" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="36" t="s">
+      <c r="D8" s="33" t="s">
         <v>26</v>
       </c>
       <c r="E8" s="9" t="s">
@@ -2256,22 +2305,22 @@
       <c r="J8" s="9" t="s">
         <v>228</v>
       </c>
-      <c r="K8" s="17" t="s">
+      <c r="K8" s="15" t="s">
         <v>229</v>
       </c>
-      <c r="L8" s="10">
-        <v>10</v>
-      </c>
-      <c r="M8" s="13">
-        <v>1</v>
-      </c>
-      <c r="N8" s="13">
-        <v>1</v>
-      </c>
-      <c r="O8" s="13">
-        <v>1</v>
-      </c>
-      <c r="P8" s="13">
+      <c r="L8" s="39">
+        <v>10</v>
+      </c>
+      <c r="M8" s="41">
+        <v>1</v>
+      </c>
+      <c r="N8" s="41">
+        <v>1</v>
+      </c>
+      <c r="O8" s="41">
+        <v>1</v>
+      </c>
+      <c r="P8" s="41">
         <v>1</v>
       </c>
     </row>
@@ -2279,13 +2328,13 @@
       <c r="A9" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="B9" s="23" t="s">
+      <c r="B9" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="39" t="s">
+      <c r="C9" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="36" t="s">
+      <c r="D9" s="33" t="s">
         <v>29</v>
       </c>
       <c r="E9" s="9" t="s">
@@ -2302,20 +2351,20 @@
       <c r="J9" s="9" t="s">
         <v>233</v>
       </c>
-      <c r="K9" s="15">
+      <c r="K9" s="13">
         <v>0.95</v>
       </c>
-      <c r="L9" s="10">
-        <v>10</v>
-      </c>
-      <c r="M9" s="13"/>
-      <c r="N9" s="13">
-        <v>1</v>
-      </c>
-      <c r="O9" s="13">
-        <v>1</v>
-      </c>
-      <c r="P9" s="13">
+      <c r="L9" s="39">
+        <v>10</v>
+      </c>
+      <c r="M9" s="41"/>
+      <c r="N9" s="41">
+        <v>1</v>
+      </c>
+      <c r="O9" s="41">
+        <v>1</v>
+      </c>
+      <c r="P9" s="41">
         <v>1</v>
       </c>
     </row>
@@ -2323,13 +2372,13 @@
       <c r="A10" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="B10" s="23" t="s">
+      <c r="B10" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="39" t="s">
+      <c r="C10" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="D10" s="36" t="s">
+      <c r="D10" s="33" t="s">
         <v>32</v>
       </c>
       <c r="E10" s="9" t="s">
@@ -2346,32 +2395,32 @@
       <c r="J10" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="K10" s="15">
+      <c r="K10" s="13">
         <v>0.95</v>
       </c>
-      <c r="L10" s="10">
-        <v>10</v>
-      </c>
-      <c r="M10" s="13"/>
-      <c r="N10" s="13">
-        <v>1</v>
-      </c>
-      <c r="O10" s="13">
-        <v>1</v>
-      </c>
-      <c r="P10" s="13"/>
+      <c r="L10" s="39">
+        <v>10</v>
+      </c>
+      <c r="M10" s="41"/>
+      <c r="N10" s="41">
+        <v>1</v>
+      </c>
+      <c r="O10" s="41">
+        <v>1</v>
+      </c>
+      <c r="P10" s="41"/>
     </row>
     <row r="11" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="B11" s="23" t="s">
+      <c r="B11" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="39" t="s">
+      <c r="C11" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="D11" s="36" t="s">
+      <c r="D11" s="33" t="s">
         <v>36</v>
       </c>
       <c r="E11" s="9" t="s">
@@ -2384,20 +2433,20 @@
       <c r="H11" s="9"/>
       <c r="I11" s="9"/>
       <c r="J11" s="9"/>
-      <c r="K11" s="15">
+      <c r="K11" s="13">
         <v>0.8</v>
       </c>
-      <c r="L11" s="10">
-        <v>10</v>
-      </c>
-      <c r="M11" s="13"/>
-      <c r="N11" s="13">
-        <v>1</v>
-      </c>
-      <c r="O11" s="13">
-        <v>1</v>
-      </c>
-      <c r="P11" s="13">
+      <c r="L11" s="39">
+        <v>10</v>
+      </c>
+      <c r="M11" s="41"/>
+      <c r="N11" s="41">
+        <v>1</v>
+      </c>
+      <c r="O11" s="41">
+        <v>1</v>
+      </c>
+      <c r="P11" s="41">
         <v>1</v>
       </c>
     </row>
@@ -2405,39 +2454,39 @@
       <c r="A12" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="B12" s="23" t="s">
+      <c r="B12" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="39" t="s">
+      <c r="C12" s="36" t="s">
         <v>38</v>
       </c>
-      <c r="D12" s="36" t="s">
+      <c r="D12" s="33" t="s">
         <v>39</v>
       </c>
       <c r="E12" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="F12" s="21" t="s">
+      <c r="F12" s="19" t="s">
         <v>241</v>
       </c>
       <c r="G12" s="9"/>
       <c r="H12" s="9"/>
       <c r="I12" s="9"/>
       <c r="J12" s="9"/>
-      <c r="K12" s="15">
+      <c r="K12" s="13">
         <v>0.8</v>
       </c>
-      <c r="L12" s="10">
-        <v>10</v>
-      </c>
-      <c r="M12" s="13"/>
-      <c r="N12" s="13">
-        <v>1</v>
-      </c>
-      <c r="O12" s="13">
-        <v>1</v>
-      </c>
-      <c r="P12" s="13">
+      <c r="L12" s="39">
+        <v>10</v>
+      </c>
+      <c r="M12" s="41"/>
+      <c r="N12" s="41">
+        <v>1</v>
+      </c>
+      <c r="O12" s="41">
+        <v>1</v>
+      </c>
+      <c r="P12" s="41">
         <v>1</v>
       </c>
     </row>
@@ -2445,19 +2494,19 @@
       <c r="A13" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="B13" s="23" t="s">
+      <c r="B13" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="C13" s="39" t="s">
+      <c r="C13" s="36" t="s">
         <v>42</v>
       </c>
-      <c r="D13" s="38" t="s">
+      <c r="D13" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="E13" s="22" t="s">
+      <c r="E13" s="20" t="s">
         <v>242</v>
       </c>
-      <c r="F13" s="22" t="s">
+      <c r="F13" s="20" t="s">
         <v>243</v>
       </c>
       <c r="G13" s="9"/>
@@ -2468,20 +2517,20 @@
       <c r="J13" s="9" t="s">
         <v>245</v>
       </c>
-      <c r="K13" s="15">
+      <c r="K13" s="13">
         <v>0.8</v>
       </c>
-      <c r="L13" s="10">
-        <v>10</v>
-      </c>
-      <c r="M13" s="13"/>
-      <c r="N13" s="13">
-        <v>1</v>
-      </c>
-      <c r="O13" s="13">
-        <v>1</v>
-      </c>
-      <c r="P13" s="13">
+      <c r="L13" s="39">
+        <v>10</v>
+      </c>
+      <c r="M13" s="41"/>
+      <c r="N13" s="41">
+        <v>1</v>
+      </c>
+      <c r="O13" s="41">
+        <v>1</v>
+      </c>
+      <c r="P13" s="41">
         <v>1</v>
       </c>
     </row>
@@ -2489,13 +2538,13 @@
       <c r="A14" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="B14" s="23" t="s">
+      <c r="B14" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="C14" s="39" t="s">
+      <c r="C14" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="D14" s="36" t="s">
+      <c r="D14" s="33" t="s">
         <v>46</v>
       </c>
       <c r="E14" s="9" t="s">
@@ -2512,22 +2561,22 @@
       <c r="J14" s="9" t="s">
         <v>249</v>
       </c>
-      <c r="K14" s="17">
+      <c r="K14" s="15">
         <v>0.4</v>
       </c>
-      <c r="L14" s="10">
-        <v>10</v>
-      </c>
-      <c r="M14" s="13">
-        <v>1</v>
-      </c>
-      <c r="N14" s="13">
-        <v>1</v>
-      </c>
-      <c r="O14" s="13">
-        <v>1</v>
-      </c>
-      <c r="P14" s="13">
+      <c r="L14" s="39">
+        <v>10</v>
+      </c>
+      <c r="M14" s="41">
+        <v>1</v>
+      </c>
+      <c r="N14" s="41">
+        <v>1</v>
+      </c>
+      <c r="O14" s="41">
+        <v>1</v>
+      </c>
+      <c r="P14" s="41">
         <v>1</v>
       </c>
     </row>
@@ -2535,13 +2584,13 @@
       <c r="A15" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="B15" s="23" t="s">
+      <c r="B15" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="C15" s="39" t="s">
+      <c r="C15" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="D15" s="36" t="s">
+      <c r="D15" s="33" t="s">
         <v>49</v>
       </c>
       <c r="E15" s="9" t="s">
@@ -2554,20 +2603,20 @@
       <c r="H15" s="9"/>
       <c r="I15" s="9"/>
       <c r="J15" s="9"/>
-      <c r="K15" s="15" t="s">
+      <c r="K15" s="13" t="s">
         <v>252</v>
       </c>
-      <c r="L15" s="10">
-        <v>10</v>
-      </c>
-      <c r="M15" s="13"/>
-      <c r="N15" s="13">
-        <v>1</v>
-      </c>
-      <c r="O15" s="13">
-        <v>1</v>
-      </c>
-      <c r="P15" s="13">
+      <c r="L15" s="39">
+        <v>10</v>
+      </c>
+      <c r="M15" s="41"/>
+      <c r="N15" s="41">
+        <v>1</v>
+      </c>
+      <c r="O15" s="41">
+        <v>1</v>
+      </c>
+      <c r="P15" s="41">
         <v>1</v>
       </c>
     </row>
@@ -2575,13 +2624,13 @@
       <c r="A16" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B16" s="23" t="s">
+      <c r="B16" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="C16" s="39" t="s">
+      <c r="C16" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="D16" s="36" t="s">
+      <c r="D16" s="33" t="s">
         <v>53</v>
       </c>
       <c r="E16" s="9" t="s">
@@ -2598,20 +2647,20 @@
       <c r="J16" s="9" t="s">
         <v>256</v>
       </c>
-      <c r="K16" s="12">
+      <c r="K16" s="11">
         <v>0.5</v>
       </c>
-      <c r="L16" s="10">
-        <v>10</v>
-      </c>
-      <c r="M16" s="13"/>
-      <c r="N16" s="13">
-        <v>1</v>
-      </c>
-      <c r="O16" s="13">
-        <v>1</v>
-      </c>
-      <c r="P16" s="13">
+      <c r="L16" s="39">
+        <v>10</v>
+      </c>
+      <c r="M16" s="41"/>
+      <c r="N16" s="41">
+        <v>1</v>
+      </c>
+      <c r="O16" s="41">
+        <v>1</v>
+      </c>
+      <c r="P16" s="41">
         <v>1</v>
       </c>
     </row>
@@ -2619,19 +2668,19 @@
       <c r="A17" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B17" s="23" t="s">
+      <c r="B17" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="C17" s="39" t="s">
+      <c r="C17" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="D17" s="38" t="s">
+      <c r="D17" s="35" t="s">
         <v>56</v>
       </c>
-      <c r="E17" s="19" t="s">
+      <c r="E17" s="17" t="s">
         <v>257</v>
       </c>
-      <c r="F17" s="22" t="s">
+      <c r="F17" s="20" t="s">
         <v>258</v>
       </c>
       <c r="G17" s="9"/>
@@ -2642,22 +2691,20 @@
       <c r="J17" s="9" t="s">
         <v>260</v>
       </c>
-      <c r="K17" s="15">
+      <c r="K17" s="13">
         <v>0.3</v>
       </c>
-      <c r="L17" s="10">
-        <v>10</v>
-      </c>
-      <c r="M17" s="13">
-        <v>1</v>
-      </c>
-      <c r="N17" s="13">
-        <v>1</v>
-      </c>
-      <c r="O17" s="13">
-        <v>1</v>
-      </c>
-      <c r="P17" s="13">
+      <c r="L17" s="39">
+        <v>10</v>
+      </c>
+      <c r="M17" s="41"/>
+      <c r="N17" s="41">
+        <v>0.7</v>
+      </c>
+      <c r="O17" s="41">
+        <v>1</v>
+      </c>
+      <c r="P17" s="41">
         <v>1</v>
       </c>
     </row>
@@ -2665,13 +2712,13 @@
       <c r="A18" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B18" s="23" t="s">
+      <c r="B18" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="C18" s="39" t="s">
+      <c r="C18" s="36" t="s">
         <v>58</v>
       </c>
-      <c r="D18" s="36" t="s">
+      <c r="D18" s="33" t="s">
         <v>59</v>
       </c>
       <c r="E18" s="9" t="s">
@@ -2688,34 +2735,30 @@
       <c r="J18" s="9" t="s">
         <v>264</v>
       </c>
-      <c r="K18" s="12">
+      <c r="K18" s="11">
         <v>0.1</v>
       </c>
-      <c r="L18" s="10">
-        <v>10</v>
-      </c>
-      <c r="M18" s="13"/>
-      <c r="N18" s="13">
-        <v>1</v>
-      </c>
-      <c r="O18" s="13">
-        <v>1</v>
-      </c>
-      <c r="P18" s="13">
-        <v>1</v>
-      </c>
+      <c r="L18" s="39">
+        <v>10</v>
+      </c>
+      <c r="M18" s="41"/>
+      <c r="N18" s="41">
+        <v>4</v>
+      </c>
+      <c r="O18" s="41"/>
+      <c r="P18" s="41"/>
     </row>
     <row r="19" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B19" s="23" t="s">
+      <c r="B19" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="C19" s="39" t="s">
+      <c r="C19" s="36" t="s">
         <v>61</v>
       </c>
-      <c r="D19" s="36" t="s">
+      <c r="D19" s="33" t="s">
         <v>62</v>
       </c>
       <c r="E19" s="9" t="s">
@@ -2728,36 +2771,28 @@
       <c r="H19" s="9"/>
       <c r="I19" s="9"/>
       <c r="J19" s="9"/>
-      <c r="K19" s="12">
+      <c r="K19" s="11">
         <v>0.1</v>
       </c>
-      <c r="L19" s="10">
-        <v>10</v>
-      </c>
-      <c r="M19" s="13">
-        <v>1</v>
-      </c>
-      <c r="N19" s="13">
-        <v>1</v>
-      </c>
-      <c r="O19" s="13">
-        <v>1</v>
-      </c>
-      <c r="P19" s="13">
-        <v>1</v>
-      </c>
+      <c r="L19" s="39">
+        <v>20</v>
+      </c>
+      <c r="M19" s="41"/>
+      <c r="N19" s="41"/>
+      <c r="O19" s="41"/>
+      <c r="P19" s="41"/>
     </row>
     <row r="20" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B20" s="23" t="s">
+      <c r="B20" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="C20" s="39" t="s">
+      <c r="C20" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="D20" s="36" t="s">
+      <c r="D20" s="33" t="s">
         <v>65</v>
       </c>
       <c r="E20" s="9" t="s">
@@ -2770,34 +2805,28 @@
       <c r="H20" s="9"/>
       <c r="I20" s="9"/>
       <c r="J20" s="9"/>
-      <c r="K20" s="12">
+      <c r="K20" s="11">
         <v>0.1</v>
       </c>
-      <c r="L20" s="10">
-        <v>10</v>
-      </c>
-      <c r="M20" s="13"/>
-      <c r="N20" s="13">
-        <v>1</v>
-      </c>
-      <c r="O20" s="13">
-        <v>1</v>
-      </c>
-      <c r="P20" s="13">
-        <v>1</v>
-      </c>
+      <c r="L20" s="39">
+        <v>10</v>
+      </c>
+      <c r="M20" s="41"/>
+      <c r="N20" s="41"/>
+      <c r="O20" s="41"/>
+      <c r="P20" s="41"/>
     </row>
     <row r="21" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B21" s="23" t="s">
+      <c r="B21" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="C21" s="39" t="s">
+      <c r="C21" s="36" t="s">
         <v>67</v>
       </c>
-      <c r="D21" s="36" t="s">
+      <c r="D21" s="33" t="s">
         <v>68</v>
       </c>
       <c r="E21" s="9" t="s">
@@ -2810,64 +2839,58 @@
       <c r="H21" s="9"/>
       <c r="I21" s="9"/>
       <c r="J21" s="9"/>
-      <c r="K21" s="12">
+      <c r="K21" s="11">
         <v>0.1</v>
       </c>
-      <c r="L21" s="10">
-        <v>10</v>
-      </c>
-      <c r="M21" s="13"/>
-      <c r="N21" s="13">
-        <v>1</v>
-      </c>
-      <c r="O21" s="13">
-        <v>1</v>
-      </c>
-      <c r="P21" s="13">
-        <v>1</v>
-      </c>
+      <c r="L21" s="39">
+        <v>10</v>
+      </c>
+      <c r="M21" s="41"/>
+      <c r="N21" s="41"/>
+      <c r="O21" s="41"/>
+      <c r="P21" s="41"/>
     </row>
     <row r="22" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="B22" s="23" t="s">
+      <c r="B22" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="C22" s="39" t="s">
+      <c r="C22" s="36" t="s">
         <v>71</v>
       </c>
-      <c r="D22" s="38" t="s">
+      <c r="D22" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="E22" s="19" t="s">
+      <c r="E22" s="17" t="s">
         <v>271</v>
       </c>
-      <c r="F22" s="22" t="s">
+      <c r="F22" s="20" t="s">
         <v>272</v>
       </c>
       <c r="G22" s="9"/>
       <c r="H22" s="9"/>
-      <c r="I22" s="23" t="s">
+      <c r="I22" s="21" t="s">
         <v>273</v>
       </c>
-      <c r="J22" s="23" t="s">
+      <c r="J22" s="21" t="s">
         <v>274</v>
       </c>
-      <c r="K22" s="12">
+      <c r="K22" s="11">
         <v>0.999</v>
       </c>
-      <c r="L22" s="10">
-        <v>10</v>
-      </c>
-      <c r="M22" s="13"/>
-      <c r="N22" s="13">
+      <c r="L22" s="39">
+        <v>10</v>
+      </c>
+      <c r="M22" s="41"/>
+      <c r="N22" s="41">
         <v>0.9</v>
       </c>
-      <c r="O22" s="13">
+      <c r="O22" s="41">
         <v>0.9</v>
       </c>
-      <c r="P22" s="13">
+      <c r="P22" s="41">
         <v>1</v>
       </c>
     </row>
@@ -2875,13 +2898,13 @@
       <c r="A23" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="B23" s="23" t="s">
+      <c r="B23" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="C23" s="39" t="s">
+      <c r="C23" s="36" t="s">
         <v>74</v>
       </c>
-      <c r="D23" s="36" t="s">
+      <c r="D23" s="33" t="s">
         <v>75</v>
       </c>
       <c r="E23" s="9" t="s">
@@ -2895,23 +2918,23 @@
       <c r="I23" s="9" t="s">
         <v>277</v>
       </c>
-      <c r="J23" s="24" t="s">
+      <c r="J23" s="22" t="s">
         <v>278</v>
       </c>
-      <c r="K23" s="15">
+      <c r="K23" s="13">
         <v>0.95</v>
       </c>
-      <c r="L23" s="10">
-        <v>10</v>
-      </c>
-      <c r="M23" s="13"/>
-      <c r="N23" s="13">
-        <v>1</v>
-      </c>
-      <c r="O23" s="13">
-        <v>1</v>
-      </c>
-      <c r="P23" s="13">
+      <c r="L23" s="39">
+        <v>10</v>
+      </c>
+      <c r="M23" s="41"/>
+      <c r="N23" s="41">
+        <v>1</v>
+      </c>
+      <c r="O23" s="41">
+        <v>1</v>
+      </c>
+      <c r="P23" s="41">
         <v>1</v>
       </c>
     </row>
@@ -2919,43 +2942,43 @@
       <c r="A24" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="B24" s="23" t="s">
+      <c r="B24" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="C24" s="39" t="s">
+      <c r="C24" s="36" t="s">
         <v>77</v>
       </c>
-      <c r="D24" s="38" t="s">
+      <c r="D24" s="35" t="s">
         <v>78</v>
       </c>
-      <c r="E24" s="19" t="s">
+      <c r="E24" s="17" t="s">
         <v>279</v>
       </c>
-      <c r="F24" s="22" t="s">
+      <c r="F24" s="20" t="s">
         <v>280</v>
       </c>
       <c r="G24" s="9"/>
       <c r="H24" s="9"/>
-      <c r="I24" s="23" t="s">
+      <c r="I24" s="21" t="s">
         <v>281</v>
       </c>
-      <c r="J24" s="23" t="s">
+      <c r="J24" s="21" t="s">
         <v>282</v>
       </c>
-      <c r="K24" s="12">
+      <c r="K24" s="11">
         <v>0.2</v>
       </c>
-      <c r="L24" s="10">
-        <v>10</v>
-      </c>
-      <c r="M24" s="13"/>
-      <c r="N24" s="13">
+      <c r="L24" s="39">
+        <v>10</v>
+      </c>
+      <c r="M24" s="41"/>
+      <c r="N24" s="41">
         <v>0.9</v>
       </c>
-      <c r="O24" s="13">
+      <c r="O24" s="41">
         <v>0.9</v>
       </c>
-      <c r="P24" s="13">
+      <c r="P24" s="41">
         <v>1</v>
       </c>
     </row>
@@ -2963,13 +2986,13 @@
       <c r="A25" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="B25" s="23" t="s">
+      <c r="B25" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="C25" s="39" t="s">
+      <c r="C25" s="36" t="s">
         <v>80</v>
       </c>
-      <c r="D25" s="36" t="s">
+      <c r="D25" s="33" t="s">
         <v>81</v>
       </c>
       <c r="E25" s="9" t="s">
@@ -2986,20 +3009,20 @@
       <c r="J25" s="9" t="s">
         <v>286</v>
       </c>
-      <c r="K25" s="15">
+      <c r="K25" s="13">
         <v>0.1</v>
       </c>
-      <c r="L25" s="10">
-        <v>10</v>
-      </c>
-      <c r="M25" s="13"/>
-      <c r="N25" s="13">
-        <v>1</v>
-      </c>
-      <c r="O25" s="13">
-        <v>1</v>
-      </c>
-      <c r="P25" s="13">
+      <c r="L25" s="39">
+        <v>10</v>
+      </c>
+      <c r="M25" s="41"/>
+      <c r="N25" s="41">
+        <v>1</v>
+      </c>
+      <c r="O25" s="41">
+        <v>1</v>
+      </c>
+      <c r="P25" s="41">
         <v>1</v>
       </c>
     </row>
@@ -3007,13 +3030,13 @@
       <c r="A26" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="B26" s="23" t="s">
+      <c r="B26" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="C26" s="39" t="s">
+      <c r="C26" s="36" t="s">
         <v>84</v>
       </c>
-      <c r="D26" s="36" t="s">
+      <c r="D26" s="33" t="s">
         <v>85</v>
       </c>
       <c r="E26" s="9" t="s">
@@ -3026,22 +3049,22 @@
       <c r="H26" s="9"/>
       <c r="I26" s="9"/>
       <c r="J26" s="9"/>
-      <c r="K26" s="15">
+      <c r="K26" s="13">
         <v>0.9</v>
       </c>
-      <c r="L26" s="10">
-        <v>10</v>
-      </c>
-      <c r="M26" s="13">
-        <v>1</v>
-      </c>
-      <c r="N26" s="13">
-        <v>1</v>
-      </c>
-      <c r="O26" s="13">
-        <v>1</v>
-      </c>
-      <c r="P26" s="13">
+      <c r="L26" s="39">
+        <v>10</v>
+      </c>
+      <c r="M26" s="41">
+        <v>1</v>
+      </c>
+      <c r="N26" s="41">
+        <v>1</v>
+      </c>
+      <c r="O26" s="41">
+        <v>1</v>
+      </c>
+      <c r="P26" s="41">
         <v>1</v>
       </c>
     </row>
@@ -3049,13 +3072,13 @@
       <c r="A27" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="B27" s="23" t="s">
+      <c r="B27" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="C27" s="39" t="s">
+      <c r="C27" s="36" t="s">
         <v>87</v>
       </c>
-      <c r="D27" s="36" t="s">
+      <c r="D27" s="33" t="s">
         <v>88</v>
       </c>
       <c r="E27" s="9" t="s">
@@ -3068,22 +3091,22 @@
       <c r="H27" s="9"/>
       <c r="I27" s="9"/>
       <c r="J27" s="9"/>
-      <c r="K27" s="15" t="s">
+      <c r="K27" s="13" t="s">
         <v>291</v>
       </c>
-      <c r="L27" s="10">
-        <v>10</v>
-      </c>
-      <c r="M27" s="13">
-        <v>1</v>
-      </c>
-      <c r="N27" s="13">
-        <v>1</v>
-      </c>
-      <c r="O27" s="13">
-        <v>1</v>
-      </c>
-      <c r="P27" s="13">
+      <c r="L27" s="39">
+        <v>10</v>
+      </c>
+      <c r="M27" s="41">
+        <v>1</v>
+      </c>
+      <c r="N27" s="41">
+        <v>1</v>
+      </c>
+      <c r="O27" s="41">
+        <v>1</v>
+      </c>
+      <c r="P27" s="41">
         <v>1</v>
       </c>
     </row>
@@ -3091,13 +3114,13 @@
       <c r="A28" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="B28" s="23" t="s">
+      <c r="B28" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="C28" s="39" t="s">
+      <c r="C28" s="36" t="s">
         <v>90</v>
       </c>
-      <c r="D28" s="36" t="s">
+      <c r="D28" s="33" t="s">
         <v>91</v>
       </c>
       <c r="E28" s="9" t="s">
@@ -3110,20 +3133,20 @@
       <c r="H28" s="9"/>
       <c r="I28" s="9"/>
       <c r="J28" s="9"/>
-      <c r="K28" s="15" t="s">
+      <c r="K28" s="13" t="s">
         <v>293</v>
       </c>
-      <c r="L28" s="10">
-        <v>10</v>
-      </c>
-      <c r="M28" s="13"/>
-      <c r="N28" s="13">
-        <v>1</v>
-      </c>
-      <c r="O28" s="13">
-        <v>1</v>
-      </c>
-      <c r="P28" s="13">
+      <c r="L28" s="39">
+        <v>10</v>
+      </c>
+      <c r="M28" s="41"/>
+      <c r="N28" s="41">
+        <v>1</v>
+      </c>
+      <c r="O28" s="41">
+        <v>1</v>
+      </c>
+      <c r="P28" s="41">
         <v>1</v>
       </c>
     </row>
@@ -3131,13 +3154,13 @@
       <c r="A29" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="B29" s="23" t="s">
+      <c r="B29" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="C29" s="39" t="s">
+      <c r="C29" s="36" t="s">
         <v>93</v>
       </c>
-      <c r="D29" s="36" t="s">
+      <c r="D29" s="33" t="s">
         <v>94</v>
       </c>
       <c r="E29" s="9" t="s">
@@ -3150,20 +3173,20 @@
       <c r="H29" s="9"/>
       <c r="I29" s="9"/>
       <c r="J29" s="9"/>
-      <c r="K29" s="15" t="s">
+      <c r="K29" s="13" t="s">
         <v>295</v>
       </c>
-      <c r="L29" s="10">
-        <v>10</v>
-      </c>
-      <c r="M29" s="13"/>
-      <c r="N29" s="13">
-        <v>1</v>
-      </c>
-      <c r="O29" s="13">
-        <v>1</v>
-      </c>
-      <c r="P29" s="13">
+      <c r="L29" s="39">
+        <v>10</v>
+      </c>
+      <c r="M29" s="41"/>
+      <c r="N29" s="41">
+        <v>1</v>
+      </c>
+      <c r="O29" s="41">
+        <v>1</v>
+      </c>
+      <c r="P29" s="41">
         <v>1</v>
       </c>
     </row>
@@ -3171,13 +3194,13 @@
       <c r="A30" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="B30" s="23" t="s">
+      <c r="B30" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="C30" s="39" t="s">
+      <c r="C30" s="36" t="s">
         <v>97</v>
       </c>
-      <c r="D30" s="36" t="s">
+      <c r="D30" s="33" t="s">
         <v>98</v>
       </c>
       <c r="E30" s="9" t="s">
@@ -3190,20 +3213,20 @@
       <c r="H30" s="9"/>
       <c r="I30" s="9"/>
       <c r="J30" s="9"/>
-      <c r="K30" s="12" t="s">
+      <c r="K30" s="11" t="s">
         <v>298</v>
       </c>
-      <c r="L30" s="10">
-        <v>10</v>
-      </c>
-      <c r="M30" s="13"/>
-      <c r="N30" s="13">
-        <v>1</v>
-      </c>
-      <c r="O30" s="13">
-        <v>1</v>
-      </c>
-      <c r="P30" s="13">
+      <c r="L30" s="39">
+        <v>10</v>
+      </c>
+      <c r="M30" s="41"/>
+      <c r="N30" s="41">
+        <v>1</v>
+      </c>
+      <c r="O30" s="41">
+        <v>1</v>
+      </c>
+      <c r="P30" s="41">
         <v>1</v>
       </c>
     </row>
@@ -3211,13 +3234,13 @@
       <c r="A31" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="B31" s="23" t="s">
+      <c r="B31" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="C31" s="39" t="s">
+      <c r="C31" s="36" t="s">
         <v>100</v>
       </c>
-      <c r="D31" s="36" t="s">
+      <c r="D31" s="33" t="s">
         <v>101</v>
       </c>
       <c r="E31" s="9" t="s">
@@ -3230,22 +3253,22 @@
       <c r="H31" s="9"/>
       <c r="I31" s="9"/>
       <c r="J31" s="9"/>
-      <c r="K31" s="15">
+      <c r="K31" s="13">
         <v>0.5</v>
       </c>
-      <c r="L31" s="10">
-        <v>10</v>
-      </c>
-      <c r="M31" s="13">
+      <c r="L31" s="39">
+        <v>10</v>
+      </c>
+      <c r="M31" s="41">
         <v>2</v>
       </c>
-      <c r="N31" s="13">
+      <c r="N31" s="41">
         <v>2</v>
       </c>
-      <c r="O31" s="13">
+      <c r="O31" s="41">
         <v>2</v>
       </c>
-      <c r="P31" s="13">
+      <c r="P31" s="41">
         <v>2</v>
       </c>
     </row>
@@ -3253,13 +3276,13 @@
       <c r="A32" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="B32" s="23" t="s">
+      <c r="B32" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="C32" s="39" t="s">
+      <c r="C32" s="36" t="s">
         <v>103</v>
       </c>
-      <c r="D32" s="36" t="s">
+      <c r="D32" s="33" t="s">
         <v>104</v>
       </c>
       <c r="E32" s="9" t="s">
@@ -3276,20 +3299,20 @@
       <c r="J32" s="9" t="s">
         <v>304</v>
       </c>
-      <c r="K32" s="15">
+      <c r="K32" s="13">
         <v>0.3</v>
       </c>
-      <c r="L32" s="10">
-        <v>10</v>
-      </c>
-      <c r="M32" s="13"/>
-      <c r="N32" s="13">
-        <v>1</v>
-      </c>
-      <c r="O32" s="13">
-        <v>1</v>
-      </c>
-      <c r="P32" s="13">
+      <c r="L32" s="39">
+        <v>10</v>
+      </c>
+      <c r="M32" s="41"/>
+      <c r="N32" s="41">
+        <v>1</v>
+      </c>
+      <c r="O32" s="41">
+        <v>1</v>
+      </c>
+      <c r="P32" s="41">
         <v>1</v>
       </c>
     </row>
@@ -3297,13 +3320,13 @@
       <c r="A33" s="9" t="s">
         <v>305</v>
       </c>
-      <c r="B33" s="23" t="s">
+      <c r="B33" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="C33" s="39" t="s">
+      <c r="C33" s="36" t="s">
         <v>107</v>
       </c>
-      <c r="D33" s="36" t="s">
+      <c r="D33" s="33" t="s">
         <v>108</v>
       </c>
       <c r="E33" s="9" t="s">
@@ -3316,20 +3339,20 @@
       <c r="H33" s="9"/>
       <c r="I33" s="9"/>
       <c r="J33" s="9"/>
-      <c r="K33" s="15">
+      <c r="K33" s="13">
         <v>0.5</v>
       </c>
-      <c r="L33" s="10">
-        <v>10</v>
-      </c>
-      <c r="M33" s="13"/>
-      <c r="N33" s="13">
-        <v>1</v>
-      </c>
-      <c r="O33" s="13">
-        <v>1</v>
-      </c>
-      <c r="P33" s="13">
+      <c r="L33" s="39">
+        <v>10</v>
+      </c>
+      <c r="M33" s="41"/>
+      <c r="N33" s="41">
+        <v>1</v>
+      </c>
+      <c r="O33" s="41">
+        <v>1</v>
+      </c>
+      <c r="P33" s="41">
         <v>1</v>
       </c>
     </row>
@@ -3337,13 +3360,13 @@
       <c r="A34" s="9" t="s">
         <v>305</v>
       </c>
-      <c r="B34" s="23" t="s">
+      <c r="B34" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="C34" s="39" t="s">
+      <c r="C34" s="36" t="s">
         <v>110</v>
       </c>
-      <c r="D34" s="36" t="s">
+      <c r="D34" s="33" t="s">
         <v>111</v>
       </c>
       <c r="E34" s="9" t="s">
@@ -3356,20 +3379,20 @@
       <c r="H34" s="9"/>
       <c r="I34" s="9"/>
       <c r="J34" s="9"/>
-      <c r="K34" s="15">
+      <c r="K34" s="13">
         <v>0.9</v>
       </c>
-      <c r="L34" s="10">
-        <v>10</v>
-      </c>
-      <c r="M34" s="13"/>
-      <c r="N34" s="13">
-        <v>1</v>
-      </c>
-      <c r="O34" s="13">
-        <v>1</v>
-      </c>
-      <c r="P34" s="13">
+      <c r="L34" s="39">
+        <v>10</v>
+      </c>
+      <c r="M34" s="41"/>
+      <c r="N34" s="41">
+        <v>1</v>
+      </c>
+      <c r="O34" s="41">
+        <v>1</v>
+      </c>
+      <c r="P34" s="41">
         <v>1</v>
       </c>
     </row>
@@ -3377,13 +3400,13 @@
       <c r="A35" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="B35" s="23" t="s">
+      <c r="B35" s="21" t="s">
         <v>113</v>
       </c>
-      <c r="C35" s="39" t="s">
+      <c r="C35" s="36" t="s">
         <v>114</v>
       </c>
-      <c r="D35" s="36" t="s">
+      <c r="D35" s="33" t="s">
         <v>115</v>
       </c>
       <c r="E35" s="9" t="s">
@@ -3396,20 +3419,20 @@
       <c r="H35" s="9"/>
       <c r="I35" s="9"/>
       <c r="J35" s="9"/>
-      <c r="K35" s="17">
+      <c r="K35" s="15">
         <v>0.5</v>
       </c>
-      <c r="L35" s="10">
-        <v>10</v>
-      </c>
-      <c r="M35" s="13"/>
-      <c r="N35" s="13">
-        <v>1</v>
-      </c>
-      <c r="O35" s="13">
-        <v>1</v>
-      </c>
-      <c r="P35" s="13">
+      <c r="L35" s="39">
+        <v>10</v>
+      </c>
+      <c r="M35" s="41"/>
+      <c r="N35" s="41">
+        <v>1</v>
+      </c>
+      <c r="O35" s="41">
+        <v>1</v>
+      </c>
+      <c r="P35" s="41">
         <v>1</v>
       </c>
     </row>
@@ -3417,13 +3440,13 @@
       <c r="A36" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="B36" s="23" t="s">
+      <c r="B36" s="21" t="s">
         <v>113</v>
       </c>
-      <c r="C36" s="39" t="s">
+      <c r="C36" s="36" t="s">
         <v>117</v>
       </c>
-      <c r="D36" s="36" t="s">
+      <c r="D36" s="33" t="s">
         <v>118</v>
       </c>
       <c r="E36" s="9" t="s">
@@ -3436,20 +3459,20 @@
       <c r="H36" s="9"/>
       <c r="I36" s="9"/>
       <c r="J36" s="9"/>
-      <c r="K36" s="15">
+      <c r="K36" s="13">
         <v>0.5</v>
       </c>
-      <c r="L36" s="10">
-        <v>10</v>
-      </c>
-      <c r="M36" s="13"/>
-      <c r="N36" s="13">
-        <v>1</v>
-      </c>
-      <c r="O36" s="13">
-        <v>1</v>
-      </c>
-      <c r="P36" s="13">
+      <c r="L36" s="39">
+        <v>10</v>
+      </c>
+      <c r="M36" s="41"/>
+      <c r="N36" s="41">
+        <v>1</v>
+      </c>
+      <c r="O36" s="41">
+        <v>1</v>
+      </c>
+      <c r="P36" s="41">
         <v>1</v>
       </c>
     </row>
@@ -3457,13 +3480,13 @@
       <c r="A37" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="B37" s="23" t="s">
+      <c r="B37" s="21" t="s">
         <v>113</v>
       </c>
-      <c r="C37" s="39" t="s">
+      <c r="C37" s="36" t="s">
         <v>120</v>
       </c>
-      <c r="D37" s="36" t="s">
+      <c r="D37" s="33" t="s">
         <v>121</v>
       </c>
       <c r="E37" s="9" t="s">
@@ -3476,20 +3499,20 @@
       <c r="H37" s="9"/>
       <c r="I37" s="9"/>
       <c r="J37" s="9"/>
-      <c r="K37" s="17">
+      <c r="K37" s="15">
         <v>0.95</v>
       </c>
-      <c r="L37" s="10">
-        <v>10</v>
-      </c>
-      <c r="M37" s="13"/>
-      <c r="N37" s="13">
-        <v>1</v>
-      </c>
-      <c r="O37" s="13">
-        <v>1</v>
-      </c>
-      <c r="P37" s="13">
+      <c r="L37" s="39">
+        <v>10</v>
+      </c>
+      <c r="M37" s="41"/>
+      <c r="N37" s="41">
+        <v>1</v>
+      </c>
+      <c r="O37" s="41">
+        <v>1</v>
+      </c>
+      <c r="P37" s="41">
         <v>1</v>
       </c>
     </row>
@@ -3497,13 +3520,13 @@
       <c r="A38" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="B38" s="23" t="s">
+      <c r="B38" s="21" t="s">
         <v>123</v>
       </c>
-      <c r="C38" s="39" t="s">
+      <c r="C38" s="36" t="s">
         <v>124</v>
       </c>
-      <c r="D38" s="36" t="s">
+      <c r="D38" s="33" t="s">
         <v>125</v>
       </c>
       <c r="E38" s="9" t="s">
@@ -3516,20 +3539,20 @@
       <c r="H38" s="9"/>
       <c r="I38" s="9"/>
       <c r="J38" s="9"/>
-      <c r="K38" s="15">
+      <c r="K38" s="13">
         <v>0.2</v>
       </c>
-      <c r="L38" s="10">
-        <v>10</v>
-      </c>
-      <c r="M38" s="13"/>
-      <c r="N38" s="13">
+      <c r="L38" s="39">
+        <v>10</v>
+      </c>
+      <c r="M38" s="41"/>
+      <c r="N38" s="41">
         <v>2</v>
       </c>
-      <c r="O38" s="13">
+      <c r="O38" s="41">
         <v>2</v>
       </c>
-      <c r="P38" s="13">
+      <c r="P38" s="41">
         <v>2</v>
       </c>
     </row>
@@ -3537,13 +3560,13 @@
       <c r="A39" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="B39" s="23" t="s">
+      <c r="B39" s="21" t="s">
         <v>123</v>
       </c>
-      <c r="C39" s="39" t="s">
+      <c r="C39" s="36" t="s">
         <v>127</v>
       </c>
-      <c r="D39" s="36" t="s">
+      <c r="D39" s="33" t="s">
         <v>128</v>
       </c>
       <c r="E39" s="9" t="s">
@@ -3556,20 +3579,20 @@
       <c r="H39" s="9"/>
       <c r="I39" s="9"/>
       <c r="J39" s="9"/>
-      <c r="K39" s="15">
+      <c r="K39" s="13">
         <v>0.2</v>
       </c>
-      <c r="L39" s="10">
-        <v>10</v>
-      </c>
-      <c r="M39" s="13"/>
-      <c r="N39" s="13">
+      <c r="L39" s="39">
+        <v>10</v>
+      </c>
+      <c r="M39" s="41"/>
+      <c r="N39" s="41">
         <v>2</v>
       </c>
-      <c r="O39" s="13">
+      <c r="O39" s="41">
         <v>2</v>
       </c>
-      <c r="P39" s="13">
+      <c r="P39" s="41">
         <v>2</v>
       </c>
     </row>
@@ -3577,13 +3600,13 @@
       <c r="A40" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="B40" s="23" t="s">
+      <c r="B40" s="21" t="s">
         <v>130</v>
       </c>
-      <c r="C40" s="39" t="s">
+      <c r="C40" s="36" t="s">
         <v>131</v>
       </c>
-      <c r="D40" s="36" t="s">
+      <c r="D40" s="33" t="s">
         <v>132</v>
       </c>
       <c r="E40" s="9" t="s">
@@ -3600,22 +3623,22 @@
       <c r="J40" s="9" t="s">
         <v>323</v>
       </c>
-      <c r="K40" s="15">
+      <c r="K40" s="13">
         <v>0.25</v>
       </c>
-      <c r="L40" s="10">
-        <v>10</v>
-      </c>
-      <c r="M40" s="13">
-        <v>1</v>
-      </c>
-      <c r="N40" s="13">
+      <c r="L40" s="39">
+        <v>10</v>
+      </c>
+      <c r="M40" s="41">
+        <v>1</v>
+      </c>
+      <c r="N40" s="41">
         <v>3</v>
       </c>
-      <c r="O40" s="13">
+      <c r="O40" s="41">
         <v>3</v>
       </c>
-      <c r="P40" s="13">
+      <c r="P40" s="41">
         <v>3</v>
       </c>
     </row>
@@ -3623,13 +3646,13 @@
       <c r="A41" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="B41" s="23" t="s">
+      <c r="B41" s="21" t="s">
         <v>134</v>
       </c>
-      <c r="C41" s="39" t="s">
+      <c r="C41" s="36" t="s">
         <v>135</v>
       </c>
-      <c r="D41" s="36" t="s">
+      <c r="D41" s="33" t="s">
         <v>136</v>
       </c>
       <c r="E41" s="9" t="s">
@@ -3639,27 +3662,27 @@
         <v>325</v>
       </c>
       <c r="G41" s="9"/>
-      <c r="H41" s="26"/>
+      <c r="H41" s="24"/>
       <c r="I41" s="9" t="s">
         <v>326</v>
       </c>
       <c r="J41" s="9" t="s">
         <v>327</v>
       </c>
-      <c r="K41" s="15">
+      <c r="K41" s="13">
         <v>0.25</v>
       </c>
-      <c r="L41" s="10">
-        <v>10</v>
-      </c>
-      <c r="M41" s="13"/>
-      <c r="N41" s="13">
-        <v>1</v>
-      </c>
-      <c r="O41" s="13">
-        <v>1</v>
-      </c>
-      <c r="P41" s="13">
+      <c r="L41" s="39">
+        <v>10</v>
+      </c>
+      <c r="M41" s="41"/>
+      <c r="N41" s="41">
+        <v>1</v>
+      </c>
+      <c r="O41" s="41">
+        <v>1</v>
+      </c>
+      <c r="P41" s="41">
         <v>1</v>
       </c>
     </row>
@@ -3667,13 +3690,13 @@
       <c r="A42" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="B42" s="23" t="s">
+      <c r="B42" s="21" t="s">
         <v>134</v>
       </c>
-      <c r="C42" s="39" t="s">
+      <c r="C42" s="36" t="s">
         <v>138</v>
       </c>
-      <c r="D42" s="36" t="s">
+      <c r="D42" s="33" t="s">
         <v>139</v>
       </c>
       <c r="E42" s="9" t="s">
@@ -3683,27 +3706,27 @@
         <v>329</v>
       </c>
       <c r="G42" s="9"/>
-      <c r="H42" s="26"/>
+      <c r="H42" s="24"/>
       <c r="I42" s="9" t="s">
         <v>330</v>
       </c>
       <c r="J42" s="9" t="s">
         <v>331</v>
       </c>
-      <c r="K42" s="15">
+      <c r="K42" s="13">
         <v>0.25</v>
       </c>
-      <c r="L42" s="10">
-        <v>10</v>
-      </c>
-      <c r="M42" s="13"/>
-      <c r="N42" s="13">
-        <v>1</v>
-      </c>
-      <c r="O42" s="13">
-        <v>1</v>
-      </c>
-      <c r="P42" s="13">
+      <c r="L42" s="39">
+        <v>10</v>
+      </c>
+      <c r="M42" s="41"/>
+      <c r="N42" s="41">
+        <v>1</v>
+      </c>
+      <c r="O42" s="41">
+        <v>1</v>
+      </c>
+      <c r="P42" s="41">
         <v>1</v>
       </c>
     </row>
@@ -3711,13 +3734,13 @@
       <c r="A43" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="B43" s="23" t="s">
+      <c r="B43" s="21" t="s">
         <v>134</v>
       </c>
-      <c r="C43" s="39" t="s">
+      <c r="C43" s="36" t="s">
         <v>141</v>
       </c>
-      <c r="D43" s="36" t="s">
+      <c r="D43" s="33" t="s">
         <v>142</v>
       </c>
       <c r="E43" s="9" t="s">
@@ -3730,20 +3753,20 @@
       <c r="H43" s="9"/>
       <c r="I43" s="9"/>
       <c r="J43" s="9"/>
-      <c r="K43" s="15">
+      <c r="K43" s="13">
         <v>0.25</v>
       </c>
-      <c r="L43" s="10">
-        <v>10</v>
-      </c>
-      <c r="M43" s="13"/>
-      <c r="N43" s="13">
-        <v>1</v>
-      </c>
-      <c r="O43" s="13">
-        <v>1</v>
-      </c>
-      <c r="P43" s="13">
+      <c r="L43" s="39">
+        <v>10</v>
+      </c>
+      <c r="M43" s="41"/>
+      <c r="N43" s="41">
+        <v>1</v>
+      </c>
+      <c r="O43" s="41">
+        <v>1</v>
+      </c>
+      <c r="P43" s="41">
         <v>1</v>
       </c>
     </row>
@@ -3751,13 +3774,13 @@
       <c r="A44" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="B44" s="23" t="s">
+      <c r="B44" s="21" t="s">
         <v>134</v>
       </c>
-      <c r="C44" s="39" t="s">
+      <c r="C44" s="36" t="s">
         <v>144</v>
       </c>
-      <c r="D44" s="36" t="s">
+      <c r="D44" s="33" t="s">
         <v>145</v>
       </c>
       <c r="E44" s="9" t="s">
@@ -3770,20 +3793,20 @@
       <c r="H44" s="9"/>
       <c r="I44" s="9"/>
       <c r="J44" s="9"/>
-      <c r="K44" s="15">
+      <c r="K44" s="13">
         <v>0.7</v>
       </c>
-      <c r="L44" s="10">
-        <v>10</v>
-      </c>
-      <c r="M44" s="13"/>
-      <c r="N44" s="13">
-        <v>1</v>
-      </c>
-      <c r="O44" s="13">
-        <v>1</v>
-      </c>
-      <c r="P44" s="13">
+      <c r="L44" s="39">
+        <v>10</v>
+      </c>
+      <c r="M44" s="41"/>
+      <c r="N44" s="41">
+        <v>1</v>
+      </c>
+      <c r="O44" s="41">
+        <v>1</v>
+      </c>
+      <c r="P44" s="41">
         <v>1</v>
       </c>
     </row>
@@ -3791,13 +3814,13 @@
       <c r="A45" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="B45" s="23" t="s">
+      <c r="B45" s="21" t="s">
         <v>134</v>
       </c>
-      <c r="C45" s="39" t="s">
+      <c r="C45" s="36" t="s">
         <v>147</v>
       </c>
-      <c r="D45" s="36" t="s">
+      <c r="D45" s="33" t="s">
         <v>148</v>
       </c>
       <c r="E45" s="9" t="s">
@@ -3814,20 +3837,20 @@
       <c r="J45" s="9" t="s">
         <v>339</v>
       </c>
-      <c r="K45" s="15">
+      <c r="K45" s="13">
         <v>0.7</v>
       </c>
-      <c r="L45" s="10">
-        <v>10</v>
-      </c>
-      <c r="M45" s="13"/>
-      <c r="N45" s="13">
-        <v>1</v>
-      </c>
-      <c r="O45" s="13">
-        <v>1</v>
-      </c>
-      <c r="P45" s="13">
+      <c r="L45" s="39">
+        <v>10</v>
+      </c>
+      <c r="M45" s="41"/>
+      <c r="N45" s="41">
+        <v>1</v>
+      </c>
+      <c r="O45" s="41">
+        <v>1</v>
+      </c>
+      <c r="P45" s="41">
         <v>1</v>
       </c>
     </row>
@@ -3835,13 +3858,13 @@
       <c r="A46" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="B46" s="23" t="s">
+      <c r="B46" s="21" t="s">
         <v>134</v>
       </c>
-      <c r="C46" s="39" t="s">
+      <c r="C46" s="36" t="s">
         <v>150</v>
       </c>
-      <c r="D46" s="36" t="s">
+      <c r="D46" s="33" t="s">
         <v>151</v>
       </c>
       <c r="E46" s="9" t="s">
@@ -3858,20 +3881,20 @@
       <c r="J46" s="9" t="s">
         <v>343</v>
       </c>
-      <c r="K46" s="17">
+      <c r="K46" s="15">
         <v>0.7</v>
       </c>
-      <c r="L46" s="10">
-        <v>10</v>
-      </c>
-      <c r="M46" s="13"/>
-      <c r="N46" s="13">
-        <v>1</v>
-      </c>
-      <c r="O46" s="13">
-        <v>1</v>
-      </c>
-      <c r="P46" s="13">
+      <c r="L46" s="39">
+        <v>10</v>
+      </c>
+      <c r="M46" s="41"/>
+      <c r="N46" s="41">
+        <v>1</v>
+      </c>
+      <c r="O46" s="41">
+        <v>1</v>
+      </c>
+      <c r="P46" s="41">
         <v>1</v>
       </c>
     </row>
@@ -3879,13 +3902,13 @@
       <c r="A47" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="B47" s="23" t="s">
+      <c r="B47" s="21" t="s">
         <v>134</v>
       </c>
-      <c r="C47" s="39" t="s">
+      <c r="C47" s="36" t="s">
         <v>153</v>
       </c>
-      <c r="D47" s="36" t="s">
+      <c r="D47" s="33" t="s">
         <v>154</v>
       </c>
       <c r="E47" s="9" t="s">
@@ -3898,22 +3921,22 @@
       <c r="H47" s="9"/>
       <c r="I47" s="9"/>
       <c r="J47" s="9"/>
-      <c r="K47" s="15">
+      <c r="K47" s="13">
         <v>0.25</v>
       </c>
-      <c r="L47" s="10">
-        <v>10</v>
-      </c>
-      <c r="M47" s="13">
-        <v>1</v>
-      </c>
-      <c r="N47" s="13">
-        <v>1</v>
-      </c>
-      <c r="O47" s="13">
-        <v>1</v>
-      </c>
-      <c r="P47" s="13">
+      <c r="L47" s="39">
+        <v>10</v>
+      </c>
+      <c r="M47" s="41">
+        <v>1</v>
+      </c>
+      <c r="N47" s="41">
+        <v>1</v>
+      </c>
+      <c r="O47" s="41">
+        <v>1</v>
+      </c>
+      <c r="P47" s="41">
         <v>1</v>
       </c>
     </row>
@@ -3921,13 +3944,13 @@
       <c r="A48" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="B48" s="23" t="s">
+      <c r="B48" s="21" t="s">
         <v>134</v>
       </c>
-      <c r="C48" s="39" t="s">
+      <c r="C48" s="36" t="s">
         <v>156</v>
       </c>
-      <c r="D48" s="36" t="s">
+      <c r="D48" s="33" t="s">
         <v>157</v>
       </c>
       <c r="E48" s="9" t="s">
@@ -3944,20 +3967,20 @@
       <c r="J48" s="9" t="s">
         <v>349</v>
       </c>
-      <c r="K48" s="15">
+      <c r="K48" s="13">
         <v>0.2</v>
       </c>
-      <c r="L48" s="10">
-        <v>10</v>
-      </c>
-      <c r="M48" s="13"/>
-      <c r="N48" s="13">
-        <v>1</v>
-      </c>
-      <c r="O48" s="13">
-        <v>1</v>
-      </c>
-      <c r="P48" s="13">
+      <c r="L48" s="39">
+        <v>10</v>
+      </c>
+      <c r="M48" s="41"/>
+      <c r="N48" s="41">
+        <v>1</v>
+      </c>
+      <c r="O48" s="41">
+        <v>1</v>
+      </c>
+      <c r="P48" s="41">
         <v>1</v>
       </c>
     </row>
@@ -3965,13 +3988,13 @@
       <c r="A49" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="B49" s="23" t="s">
+      <c r="B49" s="21" t="s">
         <v>134</v>
       </c>
-      <c r="C49" s="39" t="s">
+      <c r="C49" s="36" t="s">
         <v>159</v>
       </c>
-      <c r="D49" s="36" t="s">
+      <c r="D49" s="33" t="s">
         <v>160</v>
       </c>
       <c r="E49" s="9" t="s">
@@ -3988,20 +4011,20 @@
       <c r="J49" s="9" t="s">
         <v>353</v>
       </c>
-      <c r="K49" s="15">
+      <c r="K49" s="13">
         <v>0.3</v>
       </c>
-      <c r="L49" s="10">
-        <v>10</v>
-      </c>
-      <c r="M49" s="13"/>
-      <c r="N49" s="13">
-        <v>1</v>
-      </c>
-      <c r="O49" s="13">
-        <v>1</v>
-      </c>
-      <c r="P49" s="13">
+      <c r="L49" s="39">
+        <v>10</v>
+      </c>
+      <c r="M49" s="41"/>
+      <c r="N49" s="41">
+        <v>1</v>
+      </c>
+      <c r="O49" s="41">
+        <v>1</v>
+      </c>
+      <c r="P49" s="41">
         <v>1</v>
       </c>
     </row>
@@ -4009,13 +4032,13 @@
       <c r="A50" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="B50" s="23" t="s">
+      <c r="B50" s="21" t="s">
         <v>134</v>
       </c>
-      <c r="C50" s="39" t="s">
+      <c r="C50" s="36" t="s">
         <v>162</v>
       </c>
-      <c r="D50" s="36" t="s">
+      <c r="D50" s="33" t="s">
         <v>163</v>
       </c>
       <c r="E50" s="9" t="s">
@@ -4032,20 +4055,20 @@
       <c r="J50" s="9" t="s">
         <v>357</v>
       </c>
-      <c r="K50" s="15" t="s">
+      <c r="K50" s="13" t="s">
         <v>358</v>
       </c>
-      <c r="L50" s="10">
-        <v>10</v>
-      </c>
-      <c r="M50" s="13"/>
-      <c r="N50" s="13">
-        <v>1</v>
-      </c>
-      <c r="O50" s="13">
-        <v>1</v>
-      </c>
-      <c r="P50" s="13">
+      <c r="L50" s="39">
+        <v>10</v>
+      </c>
+      <c r="M50" s="41"/>
+      <c r="N50" s="41">
+        <v>1</v>
+      </c>
+      <c r="O50" s="41">
+        <v>1</v>
+      </c>
+      <c r="P50" s="41">
         <v>1</v>
       </c>
     </row>
@@ -4053,13 +4076,13 @@
       <c r="A51" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B51" s="23" t="s">
+      <c r="B51" s="21" t="s">
         <v>165</v>
       </c>
-      <c r="C51" s="39" t="s">
+      <c r="C51" s="36" t="s">
         <v>166</v>
       </c>
-      <c r="D51" s="36" t="s">
+      <c r="D51" s="33" t="s">
         <v>167</v>
       </c>
       <c r="E51" s="9" t="s">
@@ -4072,20 +4095,20 @@
       <c r="H51" s="9"/>
       <c r="I51" s="9"/>
       <c r="J51" s="9"/>
-      <c r="K51" s="15">
+      <c r="K51" s="13">
         <v>0.85</v>
       </c>
-      <c r="L51" s="10">
-        <v>10</v>
-      </c>
-      <c r="M51" s="13"/>
-      <c r="N51" s="13">
-        <v>1</v>
-      </c>
-      <c r="O51" s="13">
-        <v>1</v>
-      </c>
-      <c r="P51" s="13">
+      <c r="L51" s="39">
+        <v>10</v>
+      </c>
+      <c r="M51" s="41"/>
+      <c r="N51" s="41">
+        <v>1</v>
+      </c>
+      <c r="O51" s="41">
+        <v>1</v>
+      </c>
+      <c r="P51" s="41">
         <v>1</v>
       </c>
     </row>
@@ -4093,13 +4116,13 @@
       <c r="A52" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B52" s="23" t="s">
+      <c r="B52" s="21" t="s">
         <v>165</v>
       </c>
-      <c r="C52" s="39" t="s">
+      <c r="C52" s="36" t="s">
         <v>169</v>
       </c>
-      <c r="D52" s="36" t="s">
+      <c r="D52" s="33" t="s">
         <v>170</v>
       </c>
       <c r="E52" s="9" t="s">
@@ -4116,20 +4139,20 @@
       <c r="J52" s="9" t="s">
         <v>364</v>
       </c>
-      <c r="K52" s="15">
+      <c r="K52" s="13">
         <v>0.9</v>
       </c>
-      <c r="L52" s="10">
-        <v>10</v>
-      </c>
-      <c r="M52" s="13"/>
-      <c r="N52" s="13">
-        <v>1</v>
-      </c>
-      <c r="O52" s="13">
-        <v>1</v>
-      </c>
-      <c r="P52" s="13">
+      <c r="L52" s="39">
+        <v>10</v>
+      </c>
+      <c r="M52" s="41"/>
+      <c r="N52" s="41">
+        <v>1</v>
+      </c>
+      <c r="O52" s="41">
+        <v>1</v>
+      </c>
+      <c r="P52" s="41">
         <v>1</v>
       </c>
     </row>
@@ -4137,13 +4160,13 @@
       <c r="A53" s="9" t="s">
         <v>365</v>
       </c>
-      <c r="B53" s="23" t="s">
+      <c r="B53" s="21" t="s">
         <v>172</v>
       </c>
-      <c r="C53" s="39" t="s">
+      <c r="C53" s="36" t="s">
         <v>173</v>
       </c>
-      <c r="D53" s="36" t="s">
+      <c r="D53" s="33" t="s">
         <v>174</v>
       </c>
       <c r="E53" s="9" t="s">
@@ -4160,20 +4183,20 @@
       <c r="J53" s="9" t="s">
         <v>369</v>
       </c>
-      <c r="K53" s="15" t="s">
+      <c r="K53" s="13" t="s">
         <v>370</v>
       </c>
-      <c r="L53" s="10">
-        <v>10</v>
-      </c>
-      <c r="M53" s="13"/>
-      <c r="N53" s="13">
-        <v>1</v>
-      </c>
-      <c r="O53" s="13">
-        <v>1</v>
-      </c>
-      <c r="P53" s="13">
+      <c r="L53" s="39">
+        <v>10</v>
+      </c>
+      <c r="M53" s="41"/>
+      <c r="N53" s="41">
+        <v>1</v>
+      </c>
+      <c r="O53" s="41">
+        <v>1</v>
+      </c>
+      <c r="P53" s="41">
         <v>1</v>
       </c>
     </row>
@@ -4181,13 +4204,13 @@
       <c r="A54" s="9" t="s">
         <v>365</v>
       </c>
-      <c r="B54" s="23" t="s">
+      <c r="B54" s="21" t="s">
         <v>172</v>
       </c>
-      <c r="C54" s="39" t="s">
+      <c r="C54" s="36" t="s">
         <v>176</v>
       </c>
-      <c r="D54" s="36" t="s">
+      <c r="D54" s="33" t="s">
         <v>177</v>
       </c>
       <c r="E54" s="9" t="s">
@@ -4204,20 +4227,20 @@
       <c r="J54" s="9" t="s">
         <v>373</v>
       </c>
-      <c r="K54" s="15" t="s">
+      <c r="K54" s="13" t="s">
         <v>374</v>
       </c>
-      <c r="L54" s="10">
-        <v>10</v>
-      </c>
-      <c r="M54" s="13"/>
-      <c r="N54" s="13">
-        <v>1</v>
-      </c>
-      <c r="O54" s="13">
-        <v>1</v>
-      </c>
-      <c r="P54" s="13">
+      <c r="L54" s="39">
+        <v>10</v>
+      </c>
+      <c r="M54" s="41"/>
+      <c r="N54" s="41">
+        <v>1</v>
+      </c>
+      <c r="O54" s="41">
+        <v>1</v>
+      </c>
+      <c r="P54" s="41">
         <v>1</v>
       </c>
     </row>
@@ -4225,13 +4248,13 @@
       <c r="A55" s="9" t="s">
         <v>365</v>
       </c>
-      <c r="B55" s="23" t="s">
+      <c r="B55" s="21" t="s">
         <v>172</v>
       </c>
-      <c r="C55" s="39" t="s">
+      <c r="C55" s="36" t="s">
         <v>179</v>
       </c>
-      <c r="D55" s="36" t="s">
+      <c r="D55" s="33" t="s">
         <v>180</v>
       </c>
       <c r="E55" s="9" t="s">
@@ -4248,20 +4271,20 @@
       <c r="J55" s="9" t="s">
         <v>377</v>
       </c>
-      <c r="K55" s="15" t="s">
+      <c r="K55" s="13" t="s">
         <v>378</v>
       </c>
-      <c r="L55" s="10">
-        <v>10</v>
-      </c>
-      <c r="M55" s="13"/>
-      <c r="N55" s="13">
-        <v>1</v>
-      </c>
-      <c r="O55" s="13">
-        <v>1</v>
-      </c>
-      <c r="P55" s="13">
+      <c r="L55" s="39">
+        <v>10</v>
+      </c>
+      <c r="M55" s="41"/>
+      <c r="N55" s="41">
+        <v>1</v>
+      </c>
+      <c r="O55" s="41">
+        <v>1</v>
+      </c>
+      <c r="P55" s="41">
         <v>1</v>
       </c>
     </row>
@@ -4269,13 +4292,13 @@
       <c r="A56" s="9" t="s">
         <v>365</v>
       </c>
-      <c r="B56" s="23" t="s">
+      <c r="B56" s="21" t="s">
         <v>182</v>
       </c>
-      <c r="C56" s="39" t="s">
+      <c r="C56" s="36" t="s">
         <v>183</v>
       </c>
-      <c r="D56" s="36" t="s">
+      <c r="D56" s="33" t="s">
         <v>184</v>
       </c>
       <c r="E56" s="9" t="s">
@@ -4292,20 +4315,20 @@
       <c r="J56" s="9" t="s">
         <v>382</v>
       </c>
-      <c r="K56" s="15">
+      <c r="K56" s="13">
         <v>0.3</v>
       </c>
-      <c r="L56" s="10">
-        <v>10</v>
-      </c>
-      <c r="M56" s="13"/>
-      <c r="N56" s="13">
+      <c r="L56" s="39">
+        <v>10</v>
+      </c>
+      <c r="M56" s="41"/>
+      <c r="N56" s="41">
         <v>1.5</v>
       </c>
-      <c r="O56" s="13">
+      <c r="O56" s="41">
         <v>1.5</v>
       </c>
-      <c r="P56" s="13">
+      <c r="P56" s="41">
         <v>1.5</v>
       </c>
     </row>
@@ -4313,13 +4336,13 @@
       <c r="A57" s="9" t="s">
         <v>365</v>
       </c>
-      <c r="B57" s="23" t="s">
+      <c r="B57" s="21" t="s">
         <v>182</v>
       </c>
-      <c r="C57" s="39" t="s">
+      <c r="C57" s="36" t="s">
         <v>186</v>
       </c>
-      <c r="D57" s="36" t="s">
+      <c r="D57" s="33" t="s">
         <v>187</v>
       </c>
       <c r="E57" s="9" t="s">
@@ -4332,20 +4355,20 @@
       <c r="H57" s="9"/>
       <c r="I57" s="9"/>
       <c r="J57" s="9"/>
-      <c r="K57" s="12" t="s">
+      <c r="K57" s="11" t="s">
         <v>385</v>
       </c>
-      <c r="L57" s="10">
-        <v>10</v>
-      </c>
-      <c r="M57" s="13"/>
-      <c r="N57" s="13">
-        <v>1</v>
-      </c>
-      <c r="O57" s="13">
-        <v>1</v>
-      </c>
-      <c r="P57" s="13">
+      <c r="L57" s="39">
+        <v>10</v>
+      </c>
+      <c r="M57" s="41"/>
+      <c r="N57" s="41">
+        <v>1</v>
+      </c>
+      <c r="O57" s="41">
+        <v>1</v>
+      </c>
+      <c r="P57" s="41">
         <v>1</v>
       </c>
     </row>
@@ -4353,19 +4376,19 @@
       <c r="A58" s="9" t="s">
         <v>365</v>
       </c>
-      <c r="B58" s="23" t="s">
+      <c r="B58" s="21" t="s">
         <v>182</v>
       </c>
-      <c r="C58" s="39" t="s">
+      <c r="C58" s="36" t="s">
         <v>189</v>
       </c>
-      <c r="D58" s="38" t="s">
+      <c r="D58" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="E58" s="19" t="s">
+      <c r="E58" s="17" t="s">
         <v>386</v>
       </c>
-      <c r="F58" s="19" t="s">
+      <c r="F58" s="17" t="s">
         <v>387</v>
       </c>
       <c r="G58" s="9"/>
@@ -4376,20 +4399,20 @@
       <c r="J58" s="9" t="s">
         <v>389</v>
       </c>
-      <c r="K58" s="12">
+      <c r="K58" s="11">
         <v>0.85</v>
       </c>
-      <c r="L58" s="10">
-        <v>10</v>
-      </c>
-      <c r="M58" s="13"/>
-      <c r="N58" s="13">
-        <v>1</v>
-      </c>
-      <c r="O58" s="13">
-        <v>1</v>
-      </c>
-      <c r="P58" s="13">
+      <c r="L58" s="39">
+        <v>10</v>
+      </c>
+      <c r="M58" s="41"/>
+      <c r="N58" s="41">
+        <v>1</v>
+      </c>
+      <c r="O58" s="41">
+        <v>1</v>
+      </c>
+      <c r="P58" s="41">
         <v>1</v>
       </c>
     </row>
@@ -4397,13 +4420,13 @@
       <c r="A59" s="9" t="s">
         <v>365</v>
       </c>
-      <c r="B59" s="23" t="s">
+      <c r="B59" s="21" t="s">
         <v>182</v>
       </c>
-      <c r="C59" s="39" t="s">
+      <c r="C59" s="36" t="s">
         <v>191</v>
       </c>
-      <c r="D59" s="36" t="s">
+      <c r="D59" s="33" t="s">
         <v>192</v>
       </c>
       <c r="E59" s="9" t="s">
@@ -4416,20 +4439,20 @@
       <c r="H59" s="9"/>
       <c r="I59" s="9"/>
       <c r="J59" s="9"/>
-      <c r="K59" s="12">
+      <c r="K59" s="11">
         <v>0.85</v>
       </c>
-      <c r="L59" s="10">
-        <v>10</v>
-      </c>
-      <c r="M59" s="13"/>
-      <c r="N59" s="13">
-        <v>1</v>
-      </c>
-      <c r="O59" s="13">
-        <v>1</v>
-      </c>
-      <c r="P59" s="13">
+      <c r="L59" s="39">
+        <v>10</v>
+      </c>
+      <c r="M59" s="41"/>
+      <c r="N59" s="41">
+        <v>1</v>
+      </c>
+      <c r="O59" s="41">
+        <v>1</v>
+      </c>
+      <c r="P59" s="41">
         <v>1</v>
       </c>
     </row>
@@ -4437,13 +4460,13 @@
       <c r="A60" s="9" t="s">
         <v>365</v>
       </c>
-      <c r="B60" s="23" t="s">
+      <c r="B60" s="21" t="s">
         <v>182</v>
       </c>
-      <c r="C60" s="39" t="s">
+      <c r="C60" s="36" t="s">
         <v>194</v>
       </c>
-      <c r="D60" s="36" t="s">
+      <c r="D60" s="33" t="s">
         <v>195</v>
       </c>
       <c r="E60" s="9" t="s">
@@ -4456,22 +4479,22 @@
       <c r="H60" s="9"/>
       <c r="I60" s="9"/>
       <c r="J60" s="9"/>
-      <c r="K60" s="12">
+      <c r="K60" s="11">
         <v>0.85</v>
       </c>
-      <c r="L60" s="10">
-        <v>10</v>
-      </c>
-      <c r="M60" s="13">
-        <v>1</v>
-      </c>
-      <c r="N60" s="13">
-        <v>1</v>
-      </c>
-      <c r="O60" s="13">
-        <v>1</v>
-      </c>
-      <c r="P60" s="13">
+      <c r="L60" s="39">
+        <v>10</v>
+      </c>
+      <c r="M60" s="41">
+        <v>1</v>
+      </c>
+      <c r="N60" s="41">
+        <v>1</v>
+      </c>
+      <c r="O60" s="41">
+        <v>1</v>
+      </c>
+      <c r="P60" s="41">
         <v>1</v>
       </c>
     </row>
@@ -4479,13 +4502,13 @@
       <c r="A61" s="9" t="s">
         <v>365</v>
       </c>
-      <c r="B61" s="23" t="s">
+      <c r="B61" s="21" t="s">
         <v>182</v>
       </c>
-      <c r="C61" s="39" t="s">
+      <c r="C61" s="36" t="s">
         <v>197</v>
       </c>
-      <c r="D61" s="36" t="s">
+      <c r="D61" s="33" t="s">
         <v>198</v>
       </c>
       <c r="E61" s="9" t="s">
@@ -4502,20 +4525,20 @@
       <c r="J61" s="9" t="s">
         <v>397</v>
       </c>
-      <c r="K61" s="27">
-        <v>1</v>
-      </c>
-      <c r="L61" s="10">
-        <v>10</v>
-      </c>
-      <c r="M61" s="13"/>
-      <c r="N61" s="13">
-        <v>1</v>
-      </c>
-      <c r="O61" s="13">
-        <v>1</v>
-      </c>
-      <c r="P61" s="13">
+      <c r="K61" s="25">
+        <v>1</v>
+      </c>
+      <c r="L61" s="39">
+        <v>10</v>
+      </c>
+      <c r="M61" s="41"/>
+      <c r="N61" s="41">
+        <v>1</v>
+      </c>
+      <c r="O61" s="41">
+        <v>1</v>
+      </c>
+      <c r="P61" s="41">
         <v>1</v>
       </c>
     </row>
@@ -4523,13 +4546,13 @@
       <c r="A62" s="9" t="s">
         <v>365</v>
       </c>
-      <c r="B62" s="23" t="s">
+      <c r="B62" s="21" t="s">
         <v>182</v>
       </c>
-      <c r="C62" s="39" t="s">
+      <c r="C62" s="36" t="s">
         <v>200</v>
       </c>
-      <c r="D62" s="36" t="s">
+      <c r="D62" s="33" t="s">
         <v>201</v>
       </c>
       <c r="E62" s="9" t="s">
@@ -4546,20 +4569,20 @@
       <c r="J62" s="9" t="s">
         <v>401</v>
       </c>
-      <c r="K62" s="15">
+      <c r="K62" s="13">
         <v>0.95</v>
       </c>
-      <c r="L62" s="10">
-        <v>10</v>
-      </c>
-      <c r="M62" s="13"/>
-      <c r="N62" s="13">
-        <v>1</v>
-      </c>
-      <c r="O62" s="13">
-        <v>1</v>
-      </c>
-      <c r="P62" s="13">
+      <c r="L62" s="39">
+        <v>10</v>
+      </c>
+      <c r="M62" s="41"/>
+      <c r="N62" s="41">
+        <v>1</v>
+      </c>
+      <c r="O62" s="41">
+        <v>1</v>
+      </c>
+      <c r="P62" s="41">
         <v>1</v>
       </c>
     </row>
@@ -4567,13 +4590,13 @@
       <c r="A63" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="B63" s="23" t="s">
+      <c r="B63" s="21" t="s">
         <v>407</v>
       </c>
-      <c r="C63" s="39" t="s">
+      <c r="C63" s="36" t="s">
         <v>406</v>
       </c>
-      <c r="D63" s="36"/>
+      <c r="D63" s="33"/>
       <c r="E63" s="9" t="s">
         <v>398</v>
       </c>
@@ -4588,32 +4611,32 @@
       <c r="J63" s="9" t="s">
         <v>401</v>
       </c>
-      <c r="K63" s="15">
+      <c r="K63" s="13">
         <v>0.8</v>
       </c>
-      <c r="L63" s="10">
-        <v>10</v>
-      </c>
-      <c r="M63" s="13"/>
-      <c r="N63" s="13">
-        <v>1</v>
-      </c>
-      <c r="O63" s="13">
-        <v>1</v>
-      </c>
-      <c r="P63" s="13"/>
+      <c r="L63" s="39">
+        <v>10</v>
+      </c>
+      <c r="M63" s="41"/>
+      <c r="N63" s="41">
+        <v>1</v>
+      </c>
+      <c r="O63" s="41">
+        <v>1</v>
+      </c>
+      <c r="P63" s="41"/>
     </row>
     <row r="64" spans="1:16" ht="52" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="B64" s="23" t="s">
+      <c r="B64" s="21" t="s">
         <v>407</v>
       </c>
-      <c r="C64" s="39" t="s">
+      <c r="C64" s="36" t="s">
         <v>413</v>
       </c>
-      <c r="D64" s="36"/>
+      <c r="D64" s="33"/>
       <c r="E64" s="9" t="s">
         <v>398</v>
       </c>
@@ -4628,87 +4651,39 @@
       <c r="J64" s="9" t="s">
         <v>401</v>
       </c>
-      <c r="K64" s="15">
+      <c r="K64" s="13">
         <v>0.8</v>
       </c>
-      <c r="L64" s="10">
-        <v>10</v>
-      </c>
-      <c r="M64" s="13"/>
-      <c r="N64" s="13"/>
-      <c r="O64" s="13"/>
-      <c r="P64" s="13"/>
+      <c r="L64" s="39">
+        <v>10</v>
+      </c>
+      <c r="M64" s="41"/>
+      <c r="N64" s="41"/>
+      <c r="O64" s="41"/>
+      <c r="P64" s="41"/>
     </row>
     <row r="65" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="16"/>
-      <c r="B65" s="16"/>
-      <c r="C65" s="16"/>
-      <c r="D65" s="16"/>
-      <c r="E65" s="16"/>
-      <c r="F65" s="16"/>
-      <c r="G65" s="16"/>
-      <c r="H65" s="16"/>
-      <c r="I65" s="16"/>
-      <c r="J65" s="16"/>
-      <c r="K65" s="29"/>
-      <c r="L65" s="28"/>
-      <c r="M65" s="25"/>
-      <c r="N65" s="25"/>
-      <c r="O65" s="25"/>
-      <c r="P65" s="25"/>
+      <c r="A65" s="14"/>
+      <c r="B65" s="14"/>
+      <c r="C65" s="14"/>
+      <c r="D65" s="14"/>
+      <c r="E65" s="14"/>
+      <c r="F65" s="14"/>
+      <c r="G65" s="14"/>
+      <c r="H65" s="14"/>
+      <c r="I65" s="14"/>
+      <c r="J65" s="14"/>
+      <c r="K65" s="27"/>
+      <c r="L65" s="26"/>
+      <c r="M65" s="23"/>
+      <c r="N65" s="23"/>
+      <c r="O65" s="23"/>
+      <c r="P65" s="23"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:P64" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <conditionalFormatting sqref="M8">
-    <cfRule type="colorScale" priority="29">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M13">
-    <cfRule type="colorScale" priority="28">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M15">
-    <cfRule type="colorScale" priority="27">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M46">
-    <cfRule type="colorScale" priority="36">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M65:M1048576 M1:M7 M47:M62 M9:M12 M14 M16:M45 M63:O64">
-    <cfRule type="colorScale" priority="76">
+  <conditionalFormatting sqref="M65:M1048576 M1">
+    <cfRule type="colorScale" priority="77">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4720,7 +4695,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="colorScale" priority="84">
+    <cfRule type="colorScale" priority="85">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4732,31 +4707,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N65:N1048576">
-    <cfRule type="colorScale" priority="24">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N2:O6 N8:O55 N57:O62">
-    <cfRule type="colorScale" priority="85">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N56:P56">
-    <cfRule type="colorScale" priority="1">
+    <cfRule type="colorScale" priority="25">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4768,7 +4719,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O65:O1048576">
-    <cfRule type="colorScale" priority="60">
+    <cfRule type="colorScale" priority="61">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4780,31 +4731,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O1:P1">
-    <cfRule type="colorScale" priority="33">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P6 P8:P55 P57:P62">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P63:P64">
-    <cfRule type="colorScale" priority="6">
+    <cfRule type="colorScale" priority="34">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4816,7 +4743,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P65:P1048576">
-    <cfRule type="colorScale" priority="5">
+    <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>

--- a/ssp_modeling/scenario_mapping/ssp_mexico_transformation_strategy_pemex_vf.xlsx
+++ b/ssp_modeling/scenario_mapping/ssp_mexico_transformation_strategy_pemex_vf.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fabianfuentes/git/ssp_mexico/ssp_modeling/scenario_mapping/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95BCC82F-D1AC-5B48-9C5F-3D727F893176}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{126FFB17-F3FF-FD46-A477-1699086A2AE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-34340" yWindow="-620" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38400" yWindow="-620" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>

--- a/ssp_modeling/scenario_mapping/ssp_mexico_transformation_strategy_pemex_vf.xlsx
+++ b/ssp_modeling/scenario_mapping/ssp_mexico_transformation_strategy_pemex_vf.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10208"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10222"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fabianfuentes/git/ssp_mexico/ssp_modeling/scenario_mapping/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{126FFB17-F3FF-FD46-A477-1699086A2AE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4991A527-52BD-E94C-8E9C-B4AB5818499A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38400" yWindow="-620" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-44440" yWindow="-7160" windowWidth="42980" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -2928,15 +2928,9 @@
         <v>10</v>
       </c>
       <c r="M23" s="41"/>
-      <c r="N23" s="41">
-        <v>1</v>
-      </c>
-      <c r="O23" s="41">
-        <v>1</v>
-      </c>
-      <c r="P23" s="41">
-        <v>1</v>
-      </c>
+      <c r="N23" s="41"/>
+      <c r="O23" s="41"/>
+      <c r="P23" s="41"/>
     </row>
     <row r="24" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="9" t="s">
@@ -3016,15 +3010,9 @@
         <v>10</v>
       </c>
       <c r="M25" s="41"/>
-      <c r="N25" s="41">
-        <v>1</v>
-      </c>
-      <c r="O25" s="41">
-        <v>1</v>
-      </c>
-      <c r="P25" s="41">
-        <v>1</v>
-      </c>
+      <c r="N25" s="41"/>
+      <c r="O25" s="41"/>
+      <c r="P25" s="41"/>
     </row>
     <row r="26" spans="1:16" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="9" t="s">
@@ -4062,15 +4050,9 @@
         <v>10</v>
       </c>
       <c r="M50" s="41"/>
-      <c r="N50" s="41">
-        <v>1</v>
-      </c>
-      <c r="O50" s="41">
-        <v>1</v>
-      </c>
-      <c r="P50" s="41">
-        <v>1</v>
-      </c>
+      <c r="N50" s="41"/>
+      <c r="O50" s="41"/>
+      <c r="P50" s="41"/>
     </row>
     <row r="51" spans="1:16" s="4" customFormat="1" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="9" t="s">
@@ -4659,7 +4641,9 @@
       </c>
       <c r="M64" s="41"/>
       <c r="N64" s="41"/>
-      <c r="O64" s="41"/>
+      <c r="O64" s="41">
+        <v>1</v>
+      </c>
       <c r="P64" s="41"/>
     </row>
     <row r="65" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
